--- a/docs/oc-regiones/venta-y-arriendo-de-computadores-y-accesorios/atacama.xlsx
+++ b/docs/oc-regiones/venta-y-arriendo-de-computadores-y-accesorios/atacama.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M58"/>
+  <dimension ref="A1:M64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>952751-18-CM25</t>
+          <t>1172445-38-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -524,27 +524,27 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-03-03</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>74.269.600-6</t>
+          <t>62.000.810-9</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>DIRECCIÓN DE ADMINISTRACIÓN DE SALUD DAS</t>
+          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -554,7 +554,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Tic Services SPA</t>
+          <t>TIC SERVICES SPA</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>3362.35</v>
+        <v>34461.92</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1171166-455-CM25</t>
+          <t>1172445-1959-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -585,12 +585,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-03-07</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -615,12 +615,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Tic Services SPA</t>
+          <t>COMPUTACION E INGENIERIA S A</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>76.423.634-3</t>
+          <t>96.693.120-5</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -630,13 +630,13 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>24552.08</v>
+        <v>3568.69</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1171166-456-CM25</t>
+          <t>4631-40-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -646,27 +646,27 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-05-20</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>62.000.810-9</t>
+          <t>69.030.200-4</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
+          <t>I MUNICIPALIDAD DE COPIAPO</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Tic Services SPA</t>
+          <t>COMERCIALIZADORA TODOTABLET SPA</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>76.423.634-3</t>
+          <t>76.292.976-7</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -691,13 +691,13 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>24552.08</v>
+        <v>3272.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1171166-457-CM25</t>
+          <t>2380-1348-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -707,27 +707,27 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>62.000.810-9</t>
+          <t>69.030.200-4</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
+          <t>I MUNICIPALIDAD DE COPIAPO</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -737,12 +737,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Tic Services SPA</t>
+          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>76.423.634-3</t>
+          <t>76.799.430-3</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>8593.23</v>
+        <v>10899.07</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2859-1560-CM25</t>
+          <t>2380-1776-CM25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -768,27 +768,27 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>71.236.700-8</t>
+          <t>69.030.200-4</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE ATACAMA</t>
+          <t>I MUNICIPALIDAD DE COPIAPO</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -798,12 +798,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Sociedad Comercial Infostore Ltda</t>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>76.131.929-9</t>
+          <t>77.474.803-2</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -813,13 +813,13 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>49479.56</v>
+        <v>9163</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1088-155-CM25</t>
+          <t>1028871-1395-CM25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -829,27 +829,27 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>61.999.330-6</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE HUASCO</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>TIC SERVICES SPA</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>76.423.634-3</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -874,13 +874,13 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>5383.56</v>
+        <v>34733.01</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2859-1623-CM25</t>
+          <t>1171166-457-CM25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -905,12 +905,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>71.236.700-8</t>
+          <t>62.000.810-9</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE ATACAMA</t>
+          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -920,12 +920,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>Tic Services SPA</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>76.423.634-3</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -935,13 +935,13 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>19554.68</v>
+        <v>8593.23</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>952751-20-CM25</t>
+          <t>1171166-456-CM25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -956,22 +956,22 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>74.269.600-6</t>
+          <t>62.000.810-9</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>DIRECCIÓN DE ADMINISTRACIÓN DE SALUD DAS</t>
+          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -996,13 +996,13 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>21538.7</v>
+        <v>24552.08</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>952751-21-CM25</t>
+          <t>1171166-455-CM25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1017,22 +1017,22 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>74.269.600-6</t>
+          <t>62.000.810-9</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>DIRECCIÓN DE ADMINISTRACIÓN DE SALUD DAS</t>
+          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Sumatec Ltda.</t>
+          <t>Tic Services SPA</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>76.367.430-4</t>
+          <t>76.423.634-3</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -1057,18 +1057,18 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>3600.8</v>
+        <v>24552.08</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2380-2656-CM25</t>
+          <t>952751-18-CM25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1078,7 +1078,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>69.030.200-4</t>
+          <t>74.269.600-6</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COPIAPO</t>
+          <t>DIRECCIÓN DE ADMINISTRACIÓN DE SALUD DAS</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1103,12 +1103,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>ALEMED SOLUCIONES INTEGRALES SPA</t>
+          <t>Tic Services SPA</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>77.727.285-3</t>
+          <t>76.423.634-3</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1118,28 +1118,28 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>62134.11</v>
+        <v>3362.35</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2859-1875-CM25</t>
+          <t>2859-1560-CM25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1164,12 +1164,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>Sociedad Comercial Infostore Ltda</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>76.131.929-9</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1179,43 +1179,43 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>7973.95</v>
+        <v>49479.56</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>1133261-201-CM25</t>
+          <t>1088-155-CM25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>62.000.810-9</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1225,12 +1225,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>77.474.803-2</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -1240,43 +1240,43 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>12814.16</v>
+        <v>5383.56</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>4631-159-CM25</t>
+          <t>2859-1623-CM25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>69.030.200-4</t>
+          <t>71.236.700-8</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COPIAPO</t>
+          <t>UNIVERSIDAD DE ATACAMA</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1286,12 +1286,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -1301,43 +1301,43 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>16944.61</v>
+        <v>19554.68</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2859-1961-CM25</t>
+          <t>952751-20-CM25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>71.236.700-8</t>
+          <t>74.269.600-6</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE ATACAMA</t>
+          <t>DIRECCIÓN DE ADMINISTRACIÓN DE SALUD DAS</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Sociedad Comercial Infostore Ltda</t>
+          <t>Tic Services SPA</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>76.131.929-9</t>
+          <t>76.423.634-3</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
@@ -1362,28 +1362,28 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>8168.52</v>
+        <v>21538.7</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>4631-160-CM25</t>
+          <t>952751-21-CM25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1393,12 +1393,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>69.030.200-4</t>
+          <t>74.269.600-6</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COPIAPO</t>
+          <t>DIRECCIÓN DE ADMINISTRACIÓN DE SALUD DAS</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1408,12 +1408,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>ALEMED SOLUCIONES INTEGRALES SPA</t>
+          <t>Sumatec Ltda.</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>77.727.285-3</t>
+          <t>76.367.430-4</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
@@ -1423,13 +1423,13 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>12588.01</v>
+        <v>3600.8</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>751-1566-CM25</t>
+          <t>2380-2656-CM25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1439,27 +1439,27 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>72.232.200-2</t>
+          <t>69.030.200-4</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE ATACAMA</t>
+          <t>I MUNICIPALIDAD DE COPIAPO</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>COMPUTACION E INGENIERIA S A</t>
+          <t>ALEMED SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>96.693.120-5</t>
+          <t>77.727.285-3</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -1484,13 +1484,13 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>7557.31</v>
+        <v>62134.11</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>1171166-498-CM25</t>
+          <t>2859-1875-CM25</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1505,7 +1505,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1515,12 +1515,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>62.000.810-9</t>
+          <t>71.236.700-8</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
+          <t>UNIVERSIDAD DE ATACAMA</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1530,12 +1530,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Tic Services SPA</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>76.423.634-3</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
@@ -1545,13 +1545,13 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>55563.12</v>
+        <v>7973.95</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2322-1936-CM25</t>
+          <t>1133261-201-CM25</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1566,7 +1566,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1576,12 +1576,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>69.030.500-3</t>
+          <t>62.000.810-9</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VALLENAR</t>
+          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1591,12 +1591,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>76.799.430-3</t>
+          <t>77.474.803-2</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
@@ -1606,13 +1606,13 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>30046.41</v>
+        <v>12814.16</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2322-1937-CM25</t>
+          <t>4631-159-CM25</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1627,22 +1627,22 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>69.030.500-3</t>
+          <t>69.030.200-4</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VALLENAR</t>
+          <t>I MUNICIPALIDAD DE COPIAPO</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1652,12 +1652,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>COMPUNOW SPA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>78.218.816-K</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
@@ -1667,13 +1667,13 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>2566.69</v>
+        <v>16944.61</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2380-100-CM26</t>
+          <t>2859-1961-CM25</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1683,27 +1683,27 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>69.030.200-4</t>
+          <t>71.236.700-8</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COPIAPO</t>
+          <t>UNIVERSIDAD DE ATACAMA</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1713,12 +1713,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>ARTEC INVERSIONES LIMITADA</t>
+          <t>Sociedad Comercial Infostore Ltda</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>76.416.101-7</t>
+          <t>76.131.929-9</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
@@ -1728,13 +1728,13 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>35329.61</v>
+        <v>8168.52</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2322-61-CM26</t>
+          <t>4631-160-CM25</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1744,27 +1744,27 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>69.030.500-3</t>
+          <t>69.030.200-4</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VALLENAR</t>
+          <t>I MUNICIPALIDAD DE COPIAPO</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Clevertec</t>
+          <t>ALEMED SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>76.330.984-3</t>
+          <t>77.727.285-3</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
@@ -1789,13 +1789,13 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>1141.44</v>
+        <v>12588.01</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2322-161-CM26</t>
+          <t>751-1566-CM25</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1805,12 +1805,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1820,12 +1820,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>69.030.500-3</t>
+          <t>72.232.200-2</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VALLENAR</t>
+          <t>GOBIERNO REGIONAL DE ATACAMA</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1835,12 +1835,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>PC FACTORY</t>
+          <t>COMPUTACION E INGENIERIA S A</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>78.885.550-8</t>
+          <t>96.693.120-5</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
@@ -1850,13 +1850,13 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>628.3200000000001</v>
+        <v>7557.31</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>1172445-30-CM26</t>
+          <t>1171166-498-CM25</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1866,12 +1866,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1896,12 +1896,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>PC FACTORY</t>
+          <t>Tic Services SPA</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>78.885.550-8</t>
+          <t>76.423.634-3</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
@@ -1911,13 +1911,13 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>3298.68</v>
+        <v>55563.12</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>1028871-194-CM26</t>
+          <t>2322-1936-CM25</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1927,12 +1927,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>61.999.330-6</t>
+          <t>69.030.500-3</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE HUASCO</t>
+          <t>I MUNICIPALIDAD DE VALLENAR</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
+          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>77.108.316-1</t>
+          <t>76.799.430-3</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
@@ -1972,13 +1972,13 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>74978.47</v>
+        <v>30046.41</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>1028871-197-CM26</t>
+          <t>2322-1937-CM25</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1988,12 +1988,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2003,12 +2003,12 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>61.999.330-6</t>
+          <t>69.030.500-3</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE HUASCO</t>
+          <t>I MUNICIPALIDAD DE VALLENAR</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2018,12 +2018,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Sociedad Comercial Infostore Ltda</t>
+          <t>COMPUNOW SPA</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>76.131.929-9</t>
+          <t>78.218.816-K</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
@@ -2033,13 +2033,13 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>24147.03</v>
+        <v>2566.69</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>4190-68-CM26</t>
+          <t>2380-100-CM26</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2049,12 +2049,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2064,12 +2064,12 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>69.030.300-0</t>
+          <t>69.030.200-4</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CALDERA</t>
+          <t>I MUNICIPALIDAD DE COPIAPO</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2079,12 +2079,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>SYSCAM TECHNOLOGIES SPA</t>
+          <t>ARTEC INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>77.137.827-7</t>
+          <t>76.416.101-7</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
@@ -2094,13 +2094,13 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>2315.47</v>
+        <v>35329.61</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2380-573-CM26</t>
+          <t>2322-61-CM26</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2110,27 +2110,27 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>69.030.200-4</t>
+          <t>69.030.500-3</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COPIAPO</t>
+          <t>I MUNICIPALIDAD DE VALLENAR</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>Clevertec</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>76.330.984-3</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
@@ -2155,13 +2155,13 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>5537.03</v>
+        <v>1141.44</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2380-624-CM26</t>
+          <t>2322-161-CM26</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2171,27 +2171,27 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>69.030.200-4</t>
+          <t>69.030.500-3</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COPIAPO</t>
+          <t>I MUNICIPALIDAD DE VALLENAR</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2201,12 +2201,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>PC FACTORY</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>78.885.550-8</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
@@ -2216,13 +2216,13 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>2011.15</v>
+        <v>628.3200000000001</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>1172445-45-CM26</t>
+          <t>1172445-30-CM26</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2262,12 +2262,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>PC FACTORY</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>78.885.550-8</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
@@ -2277,13 +2277,13 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>27517.02</v>
+        <v>3298.68</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2859-254-CM26</t>
+          <t>1028871-194-CM26</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2293,12 +2293,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2308,12 +2308,12 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>71.236.700-8</t>
+          <t>61.999.330-6</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE ATACAMA</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE HUASCO</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2323,12 +2323,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t xml:space="preserve">AURA XD SPA </t>
+          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>76.359.312-6</t>
+          <t>77.108.316-1</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
@@ -2338,13 +2338,13 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>7997.85</v>
+        <v>74978.47</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2859-255-CM26</t>
+          <t>1028871-197-CM26</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2354,12 +2354,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2369,12 +2369,12 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>71.236.700-8</t>
+          <t>61.999.330-6</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE ATACAMA</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE HUASCO</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2384,12 +2384,12 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>Sociedad Comercial Infostore Ltda</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>76.131.929-9</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
@@ -2399,13 +2399,13 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>1042.39</v>
+        <v>24147.03</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>511505-95-CM26</t>
+          <t>4190-68-CM26</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2415,12 +2415,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2430,12 +2430,12 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>71.236.700-8</t>
+          <t>69.030.300-0</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE ATACAMA</t>
+          <t>I MUNICIPALIDAD DE CALDERA</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2445,12 +2445,12 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Sumatec Ltda.</t>
+          <t>SYSCAM TECHNOLOGIES SPA</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>76.367.430-4</t>
+          <t>77.137.827-7</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
@@ -2460,13 +2460,13 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>2690.46</v>
+        <v>2315.47</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>751-169-CM26</t>
+          <t>2380-573-CM26</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2476,12 +2476,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2491,12 +2491,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>72.232.200-2</t>
+          <t>69.030.200-4</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE ATACAMA</t>
+          <t>I MUNICIPALIDAD DE COPIAPO</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
@@ -2521,13 +2521,13 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>20869.29</v>
+        <v>5537.03</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>751-171-CM26</t>
+          <t>2380-624-CM26</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2552,12 +2552,12 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>72.232.200-2</t>
+          <t>69.030.200-4</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE ATACAMA</t>
+          <t>I MUNICIPALIDAD DE COPIAPO</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2567,12 +2567,12 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
@@ -2582,13 +2582,13 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>4789.75</v>
+        <v>2011.15</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>1171166-161-CM26</t>
+          <t>1172445-45-CM26</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>76.799.430-3</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
@@ -2643,13 +2643,13 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>16922.97</v>
+        <v>27517.02</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2859-390-CM26</t>
+          <t>2859-254-CM26</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2659,12 +2659,12 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2689,12 +2689,12 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t xml:space="preserve">AURA XD SPA </t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>76.359.312-6</t>
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
@@ -2704,13 +2704,13 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>8144.36</v>
+        <v>7997.85</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2322-325-CM26</t>
+          <t>2859-255-CM26</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2720,12 +2720,12 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2735,12 +2735,12 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>69.030.500-3</t>
+          <t>71.236.700-8</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VALLENAR</t>
+          <t>UNIVERSIDAD DE ATACAMA</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
@@ -2765,13 +2765,13 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>4568.89</v>
+        <v>1042.39</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2322-327-CM26</t>
+          <t>511505-95-CM26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2781,27 +2781,27 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>69.030.500-3</t>
+          <t>71.236.700-8</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VALLENAR</t>
+          <t>UNIVERSIDAD DE ATACAMA</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>Sumatec Ltda.</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>76.367.430-4</t>
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
@@ -2826,13 +2826,13 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>1337.32</v>
+        <v>2690.46</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>1133261-63-CM26</t>
+          <t>751-169-CM26</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2847,22 +2847,22 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>62.000.810-9</t>
+          <t>72.232.200-2</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
+          <t>GOBIERNO REGIONAL DE ATACAMA</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2872,12 +2872,12 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA IGESCOM SPA</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>77.152.668-3</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
@@ -2887,13 +2887,13 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>1856.4</v>
+        <v>20869.29</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>1133261-64-CM26</t>
+          <t>751-171-CM26</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2908,22 +2908,22 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>62.000.810-9</t>
+          <t>72.232.200-2</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
+          <t>GOBIERNO REGIONAL DE ATACAMA</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2933,12 +2933,12 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>VENTA, COMPRAS DE EQUIPOS &amp; ACCESORIOS TECNOLOGICOS SPA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>77.508.642-4</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
@@ -2948,13 +2948,13 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>6675.78</v>
+        <v>4789.75</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>1133261-65-CM26</t>
+          <t>1171166-161-CM26</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2969,7 +2969,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -3009,13 +3009,13 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>2720.34</v>
+        <v>16922.97</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>5350-951-CM26</t>
+          <t>2859-390-CM26</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3030,22 +3030,22 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>69.030.500-3</t>
+          <t>71.236.700-8</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VALLENAR</t>
+          <t>UNIVERSIDAD DE ATACAMA</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3055,12 +3055,12 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K43" t="inlineStr"/>
@@ -3070,13 +3070,13 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>22176.03</v>
+        <v>8144.36</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>5350-952-CM26</t>
+          <t>2322-325-CM26</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -3131,13 +3131,13 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>4800.76</v>
+        <v>4568.89</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2380-971-CM26</t>
+          <t>2322-327-CM26</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3147,27 +3147,27 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>69.030.200-4</t>
+          <t>69.030.500-3</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COPIAPO</t>
+          <t>I MUNICIPALIDAD DE VALLENAR</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3177,12 +3177,12 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K45" t="inlineStr"/>
@@ -3192,13 +3192,13 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>755.64</v>
+        <v>1337.32</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2322-395-CM26</t>
+          <t>1133261-63-CM26</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3208,27 +3208,27 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>69.030.500-3</t>
+          <t>62.000.810-9</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VALLENAR</t>
+          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3238,12 +3238,12 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
+          <t>COMERCIALIZADORA IGESCOM SPA</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>77.108.316-1</t>
+          <t>77.152.668-3</t>
         </is>
       </c>
       <c r="K46" t="inlineStr"/>
@@ -3253,13 +3253,13 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>761.45</v>
+        <v>1856.4</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2859-459-CM26</t>
+          <t>1133261-64-CM26</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3269,12 +3269,12 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -3284,12 +3284,12 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>71.236.700-8</t>
+          <t>62.000.810-9</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE ATACAMA</t>
+          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3299,12 +3299,12 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
+          <t>VENTA, COMPRAS DE EQUIPOS &amp; ACCESORIOS TECNOLOGICOS SPA</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>76.075.901-5</t>
+          <t>77.508.642-4</t>
         </is>
       </c>
       <c r="K47" t="inlineStr"/>
@@ -3314,13 +3314,13 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>16998.51</v>
+        <v>6675.78</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2381-668-CM26</t>
+          <t>1133261-65-CM26</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3330,12 +3330,12 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -3345,12 +3345,12 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>69.030.200-4</t>
+          <t>62.000.810-9</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COPIAPO</t>
+          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3360,12 +3360,12 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
+          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>76.075.901-5</t>
+          <t>76.799.430-3</t>
         </is>
       </c>
       <c r="K48" t="inlineStr"/>
@@ -3375,13 +3375,13 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>4439.79</v>
+        <v>2720.34</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2322-417-CM26</t>
+          <t>5350-951-CM26</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3391,17 +3391,17 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -3421,12 +3421,12 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TODOCLICK SPA</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>76.977.985-K</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K49" t="inlineStr"/>
@@ -3436,13 +3436,13 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>2110.32</v>
+        <v>22176.03</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2322-448-CM26</t>
+          <t>5350-952-CM26</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3452,17 +3452,17 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -3482,12 +3482,12 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>PC FACTORY</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>78.885.550-8</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K50" t="inlineStr"/>
@@ -3497,13 +3497,13 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>828.24</v>
+        <v>4800.76</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>511505-196-CM26</t>
+          <t>2380-971-CM26</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3518,7 +3518,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>71.236.700-8</t>
+          <t>69.030.200-4</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE ATACAMA</t>
+          <t>I MUNICIPALIDAD DE COPIAPO</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -3558,13 +3558,13 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>8901.08</v>
+        <v>755.64</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2859-601-CM26</t>
+          <t>2322-395-CM26</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3579,22 +3579,22 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>71.236.700-8</t>
+          <t>69.030.500-3</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE ATACAMA</t>
+          <t>I MUNICIPALIDAD DE VALLENAR</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -3604,12 +3604,12 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>77.108.316-1</t>
         </is>
       </c>
       <c r="K52" t="inlineStr"/>
@@ -3619,13 +3619,13 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>4936.07</v>
+        <v>761.45</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2322-527-CM26</t>
+          <t>2859-459-CM26</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3635,27 +3635,27 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>69.030.500-3</t>
+          <t>71.236.700-8</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VALLENAR</t>
+          <t>UNIVERSIDAD DE ATACAMA</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3665,12 +3665,12 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>PRODATA S.A</t>
+          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>79.808.810-6</t>
+          <t>76.075.901-5</t>
         </is>
       </c>
       <c r="K53" t="inlineStr"/>
@@ -3680,13 +3680,13 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>986.15</v>
+        <v>16998.51</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2859-778-CM26</t>
+          <t>2381-668-CM26</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3696,12 +3696,12 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3711,12 +3711,12 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>71.236.700-8</t>
+          <t>69.030.200-4</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE ATACAMA</t>
+          <t>I MUNICIPALIDAD DE COPIAPO</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>ARTEC INVERSIONES LIMITADA</t>
+          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>76.416.101-7</t>
+          <t>76.075.901-5</t>
         </is>
       </c>
       <c r="K54" t="inlineStr"/>
@@ -3741,13 +3741,13 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>28355.32</v>
+        <v>4439.79</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2859-784-CM26</t>
+          <t>2322-417-CM26</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3757,12 +3757,12 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -3772,12 +3772,12 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>71.236.700-8</t>
+          <t>69.030.500-3</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE ATACAMA</t>
+          <t>I MUNICIPALIDAD DE VALLENAR</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3787,12 +3787,12 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
+          <t>COMERCIALIZADORA TODOCLICK SPA</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>77.108.316-1</t>
+          <t>76.977.985-K</t>
         </is>
       </c>
       <c r="K55" t="inlineStr"/>
@@ -3802,13 +3802,13 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>11890.24</v>
+        <v>2110.32</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>511505-275-CM26</t>
+          <t>2322-448-CM26</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3818,27 +3818,27 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>71.236.700-8</t>
+          <t>69.030.500-3</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE ATACAMA</t>
+          <t>I MUNICIPALIDAD DE VALLENAR</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>PC FACTORY</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>78.885.550-8</t>
         </is>
       </c>
       <c r="K56" t="inlineStr"/>
@@ -3863,13 +3863,13 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>2268</v>
+        <v>828.24</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2859-811-CM26</t>
+          <t>511505-196-CM26</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3879,12 +3879,12 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>76.376.530-k</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K57" t="inlineStr"/>
@@ -3924,13 +3924,13 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>4235.51</v>
+        <v>8901.08</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2859-813-CM26</t>
+          <t>2859-601-CM26</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3940,17 +3940,17 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -3970,12 +3970,12 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K58" t="inlineStr"/>
@@ -3985,6 +3985,372 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
+        <v>4936.07</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2322-527-CM26</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>69.030.500-3</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE VALLENAR</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>PRODATA S.A</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>79.808.810-6</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="n">
+        <v>986.15</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2859-778-CM26</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>71.236.700-8</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE ATACAMA</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>ARTEC INVERSIONES LIMITADA</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>76.416.101-7</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="n">
+        <v>28355.32</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2859-784-CM26</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>71.236.700-8</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE ATACAMA</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>77.108.316-1</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="n">
+        <v>11890.24</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>511505-275-CM26</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>71.236.700-8</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE ATACAMA</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>NET NOW S.A.</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>78.112.170-3</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="n">
+        <v>2268</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2859-811-CM26</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>71.236.700-8</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE ATACAMA</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>BOOKCOMPUTER</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>76.376.530-k</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="n">
+        <v>4235.51</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2859-813-CM26</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>71.236.700-8</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE ATACAMA</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>LECHNER S.A</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>78.114.650-1</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="n">
         <v>2478.96</v>
       </c>
     </row>

--- a/docs/oc-regiones/venta-y-arriendo-de-computadores-y-accesorios/atacama.xlsx
+++ b/docs/oc-regiones/venta-y-arriendo-de-computadores-y-accesorios/atacama.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Atacama" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Atacama" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M64"/>
+  <dimension ref="A1:M111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1172445-38-CM25</t>
+          <t>4192-7-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -524,12 +524,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>mar-2025</t>
+          <t>ene-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-03-03</t>
+          <t>2025-01-13</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -539,12 +539,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>62.000.810-9</t>
+          <t>69.030.300-0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
+          <t>I MUNICIPALIDAD DE CALDERA</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -554,12 +554,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>TIC SERVICES SPA</t>
+          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>76.423.634-3</t>
+          <t>77.108.316-1</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>34461.92</v>
+        <v>33584.48</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1172445-1959-CM25</t>
+          <t>3740-38-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -585,27 +585,27 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>mar-2025</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-03-07</t>
+          <t>2025-02-05</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>62.000.810-9</t>
+          <t>69.030.700-6</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
+          <t>I MUNICIPALIDAD DE HUASCO</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -615,12 +615,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>COMPUTACION E INGENIERIA S A</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>96.693.120-5</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -630,13 +630,13 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>3568.69</v>
+        <v>32899.78</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>4631-40-CM25</t>
+          <t>2380-224-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -646,12 +646,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>may-2025</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025-05-20</t>
+          <t>2025-02-10</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TODOTABLET SPA</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>76.292.976-7</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -691,13 +691,13 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>3272.5</v>
+        <v>33252.72</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2380-1348-CM25</t>
+          <t>1171166-31-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -707,27 +707,27 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>jul-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
+          <t>2025-03-03</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>69.030.200-4</t>
+          <t>62.000.810-9</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COPIAPO</t>
+          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>10899.07</v>
+        <v>7700.49</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2380-1776-CM25</t>
+          <t>1172445-38-CM25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -768,27 +768,27 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ago-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-03-03</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>69.030.200-4</t>
+          <t>62.000.810-9</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COPIAPO</t>
+          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -798,12 +798,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+          <t>TIC SERVICES SPA</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>77.474.803-2</t>
+          <t>76.423.634-3</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -813,13 +813,13 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>9163</v>
+        <v>34461.92</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1028871-1395-CM25</t>
+          <t>2380-345-CM25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -829,27 +829,27 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>oct-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025-10-09</t>
+          <t>2025-03-04</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>61.999.330-6</t>
+          <t>69.030.200-4</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE HUASCO</t>
+          <t>I MUNICIPALIDAD DE COPIAPO</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>TIC SERVICES SPA</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>76.423.634-3</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -874,13 +874,13 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>34733.01</v>
+        <v>8781.16</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>1171166-457-CM25</t>
+          <t>1172445-1957-CM25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -890,12 +890,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-03-07</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -920,12 +920,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Tic Services SPA</t>
+          <t>ESPEX INGENIERIA LIMITADA</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>76.423.634-3</t>
+          <t>77.683.370-3</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -935,13 +935,13 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>8593.23</v>
+        <v>4750.48</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1171166-456-CM25</t>
+          <t>1172445-1959-CM25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -951,12 +951,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-03-07</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -981,12 +981,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Tic Services SPA</t>
+          <t>COMPUTACION E INGENIERIA S A</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>76.423.634-3</t>
+          <t>96.693.120-5</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -996,13 +996,13 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>24552.08</v>
+        <v>3568.69</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>1171166-455-CM25</t>
+          <t>751-65-CM25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1012,12 +1012,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-03-14</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>62.000.810-9</t>
+          <t>72.232.200-2</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
+          <t>GOBIERNO REGIONAL DE ATACAMA</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Tic Services SPA</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>76.423.634-3</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -1057,13 +1057,13 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>24552.08</v>
+        <v>8553.719999999999</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>952751-18-CM25</t>
+          <t>2380-451-CM25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1073,12 +1073,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-03-17</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>74.269.600-6</t>
+          <t>69.030.200-4</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>DIRECCIÓN DE ADMINISTRACIÓN DE SALUD DAS</t>
+          <t>I MUNICIPALIDAD DE COPIAPO</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1103,12 +1103,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Tic Services SPA</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>76.423.634-3</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1118,13 +1118,13 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>3362.35</v>
+        <v>6597.15</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2859-1560-CM25</t>
+          <t>1172445-1958-CM25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1134,12 +1134,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1149,12 +1149,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>71.236.700-8</t>
+          <t>62.000.810-9</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE ATACAMA</t>
+          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1164,12 +1164,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Sociedad Comercial Infostore Ltda</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>76.131.929-9</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1179,13 +1179,13 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>49479.56</v>
+        <v>20277.6</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>1088-155-CM25</t>
+          <t>1172445-2040-CM25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1195,27 +1195,27 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>62.000.810-9</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1225,12 +1225,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>COMERCIALIZADORA TODOTABLET SPA</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>76.292.976-7</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -1240,13 +1240,13 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>5383.56</v>
+        <v>16203.52</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2859-1623-CM25</t>
+          <t>1028871-836-CM25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-04-09</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>71.236.700-8</t>
+          <t>61.999.330-6</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE ATACAMA</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE HUASCO</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1301,13 +1301,13 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>19554.68</v>
+        <v>6188</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>952751-20-CM25</t>
+          <t>1028871-837-CM25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1317,27 +1317,27 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-04-09</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>74.269.600-6</t>
+          <t>61.999.330-6</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>DIRECCIÓN DE ADMINISTRACIÓN DE SALUD DAS</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE HUASCO</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Tic Services SPA</t>
+          <t>BOOKCOMPUTER</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>76.423.634-3</t>
+          <t>76.376.530-k</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
@@ -1362,13 +1362,13 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>21538.7</v>
+        <v>14285.36</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>952751-21-CM25</t>
+          <t>1028871-838-CM25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1378,27 +1378,27 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-04-09</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>74.269.600-6</t>
+          <t>61.999.330-6</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>DIRECCIÓN DE ADMINISTRACIÓN DE SALUD DAS</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE HUASCO</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1408,12 +1408,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Sumatec Ltda.</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>76.367.430-4</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
@@ -1423,43 +1423,43 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>3600.8</v>
+        <v>19851.58</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2380-2656-CM25</t>
+          <t>2859-262-CM25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>69.030.200-4</t>
+          <t>71.236.700-8</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COPIAPO</t>
+          <t>UNIVERSIDAD DE ATACAMA</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>ALEMED SOLUCIONES INTEGRALES SPA</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>77.727.285-3</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -1484,43 +1484,43 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>62134.11</v>
+        <v>12356.96</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2859-1875-CM25</t>
+          <t>2380-785-CM25</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-04-25</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>71.236.700-8</t>
+          <t>69.030.200-4</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE ATACAMA</t>
+          <t>I MUNICIPALIDAD DE COPIAPO</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1530,12 +1530,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>ESPEX INGENIERIA LIMITADA</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>77.683.370-3</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
@@ -1545,43 +1545,43 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>7973.95</v>
+        <v>11602.5</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>1133261-201-CM25</t>
+          <t>3703-191-CM25</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-04-28</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>62.000.810-9</t>
+          <t>69.030.700-6</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
+          <t>I MUNICIPALIDAD DE HUASCO</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1591,12 +1591,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+          <t>Sumatec Ltda.</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>77.474.803-2</t>
+          <t>76.367.430-4</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
@@ -1606,43 +1606,43 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>12814.16</v>
+        <v>17758.37</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>4631-159-CM25</t>
+          <t>1172445-2110-CM25</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>69.030.200-4</t>
+          <t>62.000.810-9</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COPIAPO</t>
+          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1652,12 +1652,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>76.799.430-3</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
@@ -1667,43 +1667,43 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>16944.61</v>
+        <v>37255.93</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2859-1961-CM25</t>
+          <t>1172445-2111-CM25</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>71.236.700-8</t>
+          <t>62.000.810-9</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE ATACAMA</t>
+          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1713,12 +1713,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Sociedad Comercial Infostore Ltda</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>76.131.929-9</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
@@ -1728,43 +1728,43 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>8168.52</v>
+        <v>21479.62</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>4631-160-CM25</t>
+          <t>1171166-204-CM25</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>69.030.200-4</t>
+          <t>62.000.810-9</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COPIAPO</t>
+          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>ALEMED SOLUCIONES INTEGRALES SPA</t>
+          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>77.727.285-3</t>
+          <t>76.799.430-3</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
@@ -1789,28 +1789,28 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>12588.01</v>
+        <v>3725.59</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>751-1566-CM25</t>
+          <t>1172445-2139-CM25</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2025-05-14</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1820,12 +1820,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>72.232.200-2</t>
+          <t>62.000.810-9</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE ATACAMA</t>
+          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1835,12 +1835,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>COMPUTACION E INGENIERIA S A</t>
+          <t>COMERCIALIZADORA TODOTABLET SPA</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>96.693.120-5</t>
+          <t>76.292.976-7</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
@@ -1850,28 +1850,28 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>7557.31</v>
+        <v>7833.77</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>1171166-498-CM25</t>
+          <t>1171166-221-CM25</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-05-14</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1896,12 +1896,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Tic Services SPA</t>
+          <t>COMERCIALIZADORA TODOTABLET SPA</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>76.423.634-3</t>
+          <t>76.292.976-7</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
@@ -1911,43 +1911,43 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>55563.12</v>
+        <v>11750.66</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2322-1936-CM25</t>
+          <t>2380-979-CM25</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-05-16</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>69.030.500-3</t>
+          <t>69.030.200-4</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VALLENAR</t>
+          <t>I MUNICIPALIDAD DE COPIAPO</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
+          <t>COMERCIALIZADORA TODOTABLET SPA</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>76.799.430-3</t>
+          <t>76.292.976-7</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
@@ -1972,43 +1972,43 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>30046.41</v>
+        <v>10445.03</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2322-1937-CM25</t>
+          <t>2380-978-CM25</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-05-16</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>69.030.500-3</t>
+          <t>69.030.200-4</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VALLENAR</t>
+          <t>I MUNICIPALIDAD DE COPIAPO</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2018,12 +2018,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>COMPUNOW SPA</t>
+          <t>COMERCIALIZADORA TODOTABLET SPA</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>78.218.816-K</t>
+          <t>76.292.976-7</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
@@ -2033,28 +2033,28 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>2566.69</v>
+        <v>2777.89</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2380-100-CM26</t>
+          <t>4631-40-CM25</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2025-05-20</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2079,12 +2079,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>ARTEC INVERSIONES LIMITADA</t>
+          <t>COMERCIALIZADORA TODOTABLET SPA</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>76.416.101-7</t>
+          <t>76.292.976-7</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
@@ -2094,28 +2094,28 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>35329.61</v>
+        <v>3272.5</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2322-61-CM26</t>
+          <t>1172445-2146-CM25</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2025-05-20</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2125,12 +2125,12 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>69.030.500-3</t>
+          <t>62.000.810-9</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VALLENAR</t>
+          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Clevertec</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>76.330.984-3</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
@@ -2155,43 +2155,43 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>1141.44</v>
+        <v>4253.35</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2322-161-CM26</t>
+          <t>751-185-CM25</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>69.030.500-3</t>
+          <t>72.232.200-2</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VALLENAR</t>
+          <t>GOBIERNO REGIONAL DE ATACAMA</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2201,12 +2201,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>PC FACTORY</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>78.885.550-8</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
@@ -2216,43 +2216,43 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>628.3200000000001</v>
+        <v>39032</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>1172445-30-CM26</t>
+          <t>751-187-CM25</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2025-05-23</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>62.000.810-9</t>
+          <t>72.232.200-2</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
+          <t>GOBIERNO REGIONAL DE ATACAMA</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2262,12 +2262,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>PC FACTORY</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>78.885.550-8</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
@@ -2277,43 +2277,43 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>3298.68</v>
+        <v>3683.05</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>1028871-194-CM26</t>
+          <t>2380-1098-CM25</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2025-05-29</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>61.999.330-6</t>
+          <t>69.030.200-4</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE HUASCO</t>
+          <t>I MUNICIPALIDAD DE COPIAPO</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2323,12 +2323,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
+          <t>COMERCIALIZADORA TODOTABLET SPA</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>77.108.316-1</t>
+          <t>76.292.976-7</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
@@ -2338,43 +2338,43 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>74978.47</v>
+        <v>8181.25</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>1028871-197-CM26</t>
+          <t>2380-1099-CM25</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2025-05-29</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>61.999.330-6</t>
+          <t>69.030.200-4</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE HUASCO</t>
+          <t>I MUNICIPALIDAD DE COPIAPO</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2384,12 +2384,12 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Sociedad Comercial Infostore Ltda</t>
+          <t>COMERCIALIZADORA TODOTABLET SPA</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>76.131.929-9</t>
+          <t>76.292.976-7</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
@@ -2399,28 +2399,28 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>24147.03</v>
+        <v>2454.38</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>4190-68-CM26</t>
+          <t>2380-1105-CM25</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2025-05-30</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2430,12 +2430,12 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>69.030.300-0</t>
+          <t>69.030.200-4</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CALDERA</t>
+          <t>I MUNICIPALIDAD DE COPIAPO</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2445,12 +2445,12 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>SYSCAM TECHNOLOGIES SPA</t>
+          <t>COMERCIALIZADORA TODOTABLET SPA</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>77.137.827-7</t>
+          <t>76.292.976-7</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
@@ -2460,28 +2460,28 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>2315.47</v>
+        <v>4629.81</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2380-573-CM26</t>
+          <t>2380-1108-CM25</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>COMERCIALIZADORA TODOTABLET SPA</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>76.292.976-7</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
@@ -2521,43 +2521,43 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>5537.03</v>
+        <v>2777.89</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2380-624-CM26</t>
+          <t>2859-549-CM25</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>69.030.200-4</t>
+          <t>71.236.700-8</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COPIAPO</t>
+          <t>UNIVERSIDAD DE ATACAMA</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2567,12 +2567,12 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>ARTEC INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>76.416.101-7</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
@@ -2582,43 +2582,43 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>2011.15</v>
+        <v>4383.67</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>1172445-45-CM26</t>
+          <t>751-221-CM25</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>62.000.810-9</t>
+          <t>72.232.200-2</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
+          <t>GOBIERNO REGIONAL DE ATACAMA</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>77.474.803-2</t>
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
@@ -2643,43 +2643,43 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>27517.02</v>
+        <v>2451.4</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2859-254-CM26</t>
+          <t>2380-1430-CM25</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>71.236.700-8</t>
+          <t>69.030.200-4</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE ATACAMA</t>
+          <t>I MUNICIPALIDAD DE COPIAPO</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2689,12 +2689,12 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t xml:space="preserve">AURA XD SPA </t>
+          <t>INTEGRACION DE SOLUCIONES LIMITADA</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>76.359.312-6</t>
+          <t>76.128.275-1</t>
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
@@ -2704,43 +2704,43 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>7997.85</v>
+        <v>2809.52</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2859-255-CM26</t>
+          <t>2380-1348-CM25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>71.236.700-8</t>
+          <t>69.030.200-4</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE ATACAMA</t>
+          <t>I MUNICIPALIDAD DE COPIAPO</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>76.799.430-3</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
@@ -2765,43 +2765,43 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>1042.39</v>
+        <v>10899.07</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>511505-95-CM26</t>
+          <t>1028871-1131-CM25</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2025-07-31</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>71.236.700-8</t>
+          <t>61.999.330-6</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE ATACAMA</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE HUASCO</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Sumatec Ltda.</t>
+          <t>Sociedad Comercial Infostore Ltda</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>76.367.430-4</t>
+          <t>76.131.929-9</t>
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
@@ -2826,43 +2826,43 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>2690.46</v>
+        <v>17009.62</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>751-169-CM26</t>
+          <t>2859-893-CM25</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2025-08-13</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>72.232.200-2</t>
+          <t>71.236.700-8</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE ATACAMA</t>
+          <t>UNIVERSIDAD DE ATACAMA</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2872,12 +2872,12 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>COMERCIALIZADORA TODOTABLET SPA</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>76.292.976-7</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
@@ -2887,28 +2887,28 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>20869.29</v>
+        <v>7833.77</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>751-171-CM26</t>
+          <t>2380-1776-CM25</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2918,12 +2918,12 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>72.232.200-2</t>
+          <t>69.030.200-4</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE ATACAMA</t>
+          <t>I MUNICIPALIDAD DE COPIAPO</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2933,12 +2933,12 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>77.474.803-2</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
@@ -2948,28 +2948,28 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>4789.75</v>
+        <v>9163</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>1171166-161-CM26</t>
+          <t>1028871-1252-CM25</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2979,12 +2979,12 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>62.000.810-9</t>
+          <t>61.999.330-6</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE HUASCO</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2994,12 +2994,12 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
+          <t>TIC SERVICES SPA</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>76.799.430-3</t>
+          <t>76.423.634-3</t>
         </is>
       </c>
       <c r="K42" t="inlineStr"/>
@@ -3009,28 +3009,28 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>16922.97</v>
+        <v>11652.48</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2859-390-CM26</t>
+          <t>1028871-1250-CM25</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -3040,12 +3040,12 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>71.236.700-8</t>
+          <t>61.999.330-6</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE ATACAMA</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE HUASCO</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3055,12 +3055,12 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K43" t="inlineStr"/>
@@ -3070,28 +3070,28 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>8144.36</v>
+        <v>5941.29</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2322-325-CM26</t>
+          <t>1180885-7-CM25</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -3101,12 +3101,12 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>69.030.500-3</t>
+          <t>61.606.300-6</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VALLENAR</t>
+          <t>SERVICIO DE SALUD ATACAMA</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3116,58 +3116,62 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr"/>
+          <t>78.112.170-3</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>4568.89</v>
+        <v>89178.60000000001</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2322-327-CM26</t>
+          <t>3703-468-CM25</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>69.030.500-3</t>
+          <t>69.030.700-6</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VALLENAR</t>
+          <t>I MUNICIPALIDAD DE HUASCO</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3177,12 +3181,12 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>BOOKCOMPUTER</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>76.376.530-k</t>
         </is>
       </c>
       <c r="K45" t="inlineStr"/>
@@ -3192,28 +3196,28 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>1337.32</v>
+        <v>12255.11</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>1133261-63-CM26</t>
+          <t>1028871-1323-CM25</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -3223,12 +3227,12 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>62.000.810-9</t>
+          <t>61.999.330-6</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE HUASCO</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3238,12 +3242,12 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA IGESCOM SPA</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>77.152.668-3</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K46" t="inlineStr"/>
@@ -3253,28 +3257,28 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>1856.4</v>
+        <v>10814.72</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>1133261-64-CM26</t>
+          <t>820-34-CM25</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -3284,12 +3288,12 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>62.000.810-9</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3299,12 +3303,12 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>VENTA, COMPRAS DE EQUIPOS &amp; ACCESORIOS TECNOLOGICOS SPA</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>77.508.642-4</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K47" t="inlineStr"/>
@@ -3314,43 +3318,43 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>6675.78</v>
+        <v>3214.86</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>1133261-65-CM26</t>
+          <t>2380-2074-CM25</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>62.000.810-9</t>
+          <t>69.030.200-4</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
+          <t>I MUNICIPALIDAD DE COPIAPO</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3360,12 +3364,12 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>76.799.430-3</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K48" t="inlineStr"/>
@@ -3375,43 +3379,43 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>2720.34</v>
+        <v>3012.75</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>5350-951-CM26</t>
+          <t>820-36-CM25</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>69.030.500-3</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VALLENAR</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -3421,12 +3425,12 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>TIC SERVICES SPA</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>76.423.634-3</t>
         </is>
       </c>
       <c r="K49" t="inlineStr"/>
@@ -3436,43 +3440,43 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>22176.03</v>
+        <v>14351.4</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>5350-952-CM26</t>
+          <t>2859-1256-CM25</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>69.030.500-3</t>
+          <t>71.236.700-8</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VALLENAR</t>
+          <t>UNIVERSIDAD DE ATACAMA</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -3482,12 +3486,12 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>Sumatec Ltda.</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>76.367.430-4</t>
         </is>
       </c>
       <c r="K50" t="inlineStr"/>
@@ -3497,43 +3501,43 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>4800.76</v>
+        <v>7633.85</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2380-971-CM26</t>
+          <t>1028871-1395-CM25</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>69.030.200-4</t>
+          <t>61.999.330-6</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COPIAPO</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE HUASCO</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -3543,12 +3547,12 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>TIC SERVICES SPA</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>76.423.634-3</t>
         </is>
       </c>
       <c r="K51" t="inlineStr"/>
@@ -3558,28 +3562,28 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>755.64</v>
+        <v>34733.01</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2322-395-CM26</t>
+          <t>2381-1582-CM25</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -3589,12 +3593,12 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>69.030.500-3</t>
+          <t>69.030.200-4</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VALLENAR</t>
+          <t>I MUNICIPALIDAD DE COPIAPO</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -3604,12 +3608,12 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>77.108.316-1</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K52" t="inlineStr"/>
@@ -3619,28 +3623,28 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>761.45</v>
+        <v>8802.190000000001</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2859-459-CM26</t>
+          <t>1171166-455-CM25</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3650,12 +3654,12 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>71.236.700-8</t>
+          <t>62.000.810-9</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE ATACAMA</t>
+          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3665,12 +3669,12 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
+          <t>Tic Services SPA</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>76.075.901-5</t>
+          <t>76.423.634-3</t>
         </is>
       </c>
       <c r="K53" t="inlineStr"/>
@@ -3680,28 +3684,28 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>16998.51</v>
+        <v>24552.08</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2381-668-CM26</t>
+          <t>1171166-456-CM25</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3711,12 +3715,12 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>69.030.200-4</t>
+          <t>62.000.810-9</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COPIAPO</t>
+          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3726,12 +3730,12 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
+          <t>Tic Services SPA</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>76.075.901-5</t>
+          <t>76.423.634-3</t>
         </is>
       </c>
       <c r="K54" t="inlineStr"/>
@@ -3741,28 +3745,28 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>4439.79</v>
+        <v>24552.08</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2322-417-CM26</t>
+          <t>1171166-457-CM25</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -3772,12 +3776,12 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>69.030.500-3</t>
+          <t>62.000.810-9</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VALLENAR</t>
+          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3787,12 +3791,12 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TODOCLICK SPA</t>
+          <t>Tic Services SPA</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>76.977.985-K</t>
+          <t>76.423.634-3</t>
         </is>
       </c>
       <c r="K55" t="inlineStr"/>
@@ -3802,43 +3806,43 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>2110.32</v>
+        <v>8593.23</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2322-448-CM26</t>
+          <t>952751-18-CM25</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>69.030.500-3</t>
+          <t>74.269.600-6</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VALLENAR</t>
+          <t>DIRECCIÓN DE ADMINISTRACIÓN DE SALUD DAS</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3848,12 +3852,12 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>PC FACTORY</t>
+          <t>Tic Services SPA</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>78.885.550-8</t>
+          <t>76.423.634-3</t>
         </is>
       </c>
       <c r="K56" t="inlineStr"/>
@@ -3863,33 +3867,33 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>828.24</v>
+        <v>3362.35</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>511505-196-CM26</t>
+          <t>2859-1560-CM25</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -3909,12 +3913,12 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>Sociedad Comercial Infostore Ltda</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>76.131.929-9</t>
         </is>
       </c>
       <c r="K57" t="inlineStr"/>
@@ -3924,43 +3928,43 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>8901.08</v>
+        <v>49479.56</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2859-601-CM26</t>
+          <t>1088-155-CM25</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>71.236.700-8</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE ATACAMA</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -3970,12 +3974,12 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K58" t="inlineStr"/>
@@ -3985,43 +3989,43 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>4936.07</v>
+        <v>5383.56</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2322-527-CM26</t>
+          <t>2859-1623-CM25</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>69.030.500-3</t>
+          <t>71.236.700-8</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VALLENAR</t>
+          <t>UNIVERSIDAD DE ATACAMA</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4031,12 +4035,12 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>PRODATA S.A</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>79.808.810-6</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K59" t="inlineStr"/>
@@ -4046,43 +4050,43 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>986.15</v>
+        <v>19554.68</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2859-778-CM26</t>
+          <t>952751-20-CM25</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>71.236.700-8</t>
+          <t>74.269.600-6</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE ATACAMA</t>
+          <t>DIRECCIÓN DE ADMINISTRACIÓN DE SALUD DAS</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4092,12 +4096,12 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>ARTEC INVERSIONES LIMITADA</t>
+          <t>Tic Services SPA</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>76.416.101-7</t>
+          <t>76.423.634-3</t>
         </is>
       </c>
       <c r="K60" t="inlineStr"/>
@@ -4107,43 +4111,43 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>28355.32</v>
+        <v>21538.7</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2859-784-CM26</t>
+          <t>952751-21-CM25</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>71.236.700-8</t>
+          <t>74.269.600-6</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE ATACAMA</t>
+          <t>DIRECCIÓN DE ADMINISTRACIÓN DE SALUD DAS</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -4153,12 +4157,12 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
+          <t>Sumatec Ltda.</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>77.108.316-1</t>
+          <t>76.367.430-4</t>
         </is>
       </c>
       <c r="K61" t="inlineStr"/>
@@ -4168,13 +4172,13 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>11890.24</v>
+        <v>3600.8</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>511505-275-CM26</t>
+          <t>2380-2656-CM25</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4184,12 +4188,12 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -4199,12 +4203,12 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>71.236.700-8</t>
+          <t>69.030.200-4</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE ATACAMA</t>
+          <t>I MUNICIPALIDAD DE COPIAPO</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -4214,12 +4218,12 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>ALEMED SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>77.727.285-3</t>
         </is>
       </c>
       <c r="K62" t="inlineStr"/>
@@ -4229,13 +4233,13 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>2268</v>
+        <v>62134.11</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2859-811-CM26</t>
+          <t>2859-1875-CM25</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4245,17 +4249,17 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -4275,12 +4279,12 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>76.376.530-k</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K63" t="inlineStr"/>
@@ -4290,13 +4294,13 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>4235.51</v>
+        <v>7973.95</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2859-813-CM26</t>
+          <t>1133261-201-CM25</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4306,27 +4310,27 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>71.236.700-8</t>
+          <t>62.000.810-9</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE ATACAMA</t>
+          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -4336,12 +4340,12 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>77.474.803-2</t>
         </is>
       </c>
       <c r="K64" t="inlineStr"/>
@@ -4351,7 +4355,2874 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
+        <v>12814.16</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>4631-159-CM25</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>dic-2025</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>2025-12-16</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>69.030.200-4</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE COPIAPO</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>77.700.780-7</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="n">
+        <v>16944.61</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>4631-160-CM25</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>dic-2025</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>2025-12-17</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>69.030.200-4</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE COPIAPO</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>ALEMED SOLUCIONES INTEGRALES SPA</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>77.727.285-3</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="n">
+        <v>12588.01</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2859-1961-CM25</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>dic-2025</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>2025-12-17</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>71.236.700-8</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE ATACAMA</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>Sociedad Comercial Infostore Ltda</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>76.131.929-9</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="n">
+        <v>8168.52</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>751-1566-CM25</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>dic-2025</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>2025-12-19</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>72.232.200-2</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>GOBIERNO REGIONAL DE ATACAMA</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>COMPUTACION E INGENIERIA S A</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>96.693.120-5</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="n">
+        <v>7557.31</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>1171166-498-CM25</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>dic-2025</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>2025-12-24</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>62.000.810-9</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>Tic Services SPA</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>76.423.634-3</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="n">
+        <v>55563.12</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2322-1937-CM25</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>dic-2025</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>69.030.500-3</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE VALLENAR</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>COMPUNOW SPA</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>78.218.816-K</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="n">
+        <v>2566.69</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2322-1936-CM25</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>dic-2025</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>69.030.500-3</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE VALLENAR</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>76.799.430-3</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="n">
+        <v>30046.41</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2380-100-CM26</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>ene-2026</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>2026-01-23</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>69.030.200-4</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE COPIAPO</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>ARTEC INVERSIONES LIMITADA</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>76.416.101-7</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="n">
+        <v>35329.61</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2322-61-CM26</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>ene-2026</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>2026-01-29</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>69.030.500-3</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE VALLENAR</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>Clevertec</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>76.330.984-3</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="n">
+        <v>1141.44</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2322-161-CM26</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>69.030.500-3</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE VALLENAR</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>PC FACTORY</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>78.885.550-8</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="n">
+        <v>628.3200000000001</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>1172445-30-CM26</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>62.000.810-9</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>PC FACTORY</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>78.885.550-8</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="n">
+        <v>3298.68</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>1028871-194-CM26</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>61.999.330-6</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE HUASCO</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>77.108.316-1</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="n">
+        <v>74978.47</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>1028871-197-CM26</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>61.999.330-6</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE HUASCO</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>Sociedad Comercial Infostore Ltda</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>76.131.929-9</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="n">
+        <v>24147.03</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>4190-68-CM26</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>69.030.300-0</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CALDERA</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>SYSCAM TECHNOLOGIES SPA</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>77.137.827-7</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="n">
+        <v>2315.47</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2380-573-CM26</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>69.030.200-4</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE COPIAPO</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>NET NOW S.A.</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>78.112.170-3</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="n">
+        <v>5537.03</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2380-624-CM26</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>69.030.200-4</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE COPIAPO</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>96.678.350-8</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="n">
+        <v>2011.15</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>1172445-45-CM26</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>62.000.810-9</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>NET NOW S.A.</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>78.112.170-3</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="n">
+        <v>27517.02</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2859-254-CM26</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>71.236.700-8</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE ATACAMA</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AURA XD SPA </t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>76.359.312-6</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="n">
+        <v>7997.85</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2859-255-CM26</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>71.236.700-8</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE ATACAMA</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>LECHNER S.A</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>78.114.650-1</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="n">
+        <v>1042.39</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>511505-95-CM26</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>71.236.700-8</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE ATACAMA</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>Sumatec Ltda.</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>76.367.430-4</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="n">
+        <v>2690.46</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>751-169-CM26</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>72.232.200-2</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>GOBIERNO REGIONAL DE ATACAMA</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>LECHNER S.A</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>78.114.650-1</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="n">
+        <v>20869.29</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>751-171-CM26</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>72.232.200-2</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>GOBIERNO REGIONAL DE ATACAMA</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>77.700.780-7</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="n">
+        <v>4789.75</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>1171166-161-CM26</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>62.000.810-9</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>76.799.430-3</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="n">
+        <v>16922.97</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2859-390-CM26</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>71.236.700-8</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE ATACAMA</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>77.700.780-7</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="n">
+        <v>8144.36</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>1133261-65-CM26</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>62.000.810-9</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>76.799.430-3</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="n">
+        <v>2720.34</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>1133261-63-CM26</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>62.000.810-9</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA IGESCOM SPA</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>77.152.668-3</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="n">
+        <v>1856.4</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>1133261-64-CM26</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>62.000.810-9</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>VENTA, COMPRAS DE EQUIPOS &amp; ACCESORIOS TECNOLOGICOS SPA</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>77.508.642-4</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="n">
+        <v>6675.78</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2322-325-CM26</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>69.030.500-3</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE VALLENAR</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>77.700.780-7</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr"/>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="n">
+        <v>4568.89</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2322-327-CM26</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>69.030.500-3</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE VALLENAR</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>77.700.780-7</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="n">
+        <v>1337.32</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>5350-951-CM26</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>69.030.500-3</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE VALLENAR</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>NET NOW S.A.</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>78.112.170-3</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr"/>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="n">
+        <v>22176.03</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>5350-952-CM26</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>69.030.500-3</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE VALLENAR</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>77.700.780-7</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="n">
+        <v>4800.76</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2380-971-CM26</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>69.030.200-4</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE COPIAPO</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>NET NOW S.A.</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>78.112.170-3</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="n">
+        <v>755.64</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2322-395-CM26</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>69.030.500-3</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE VALLENAR</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>77.108.316-1</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="n">
+        <v>761.45</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2859-459-CM26</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>71.236.700-8</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE ATACAMA</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>76.075.901-5</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="n">
+        <v>16998.51</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2381-668-CM26</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>69.030.200-4</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE COPIAPO</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>76.075.901-5</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr"/>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="n">
+        <v>4439.79</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2322-417-CM26</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>69.030.500-3</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE VALLENAR</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA TODOCLICK SPA</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>76.977.985-K</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr"/>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M100" s="2" t="n">
+        <v>2110.32</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>511505-196-CM26</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>71.236.700-8</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE ATACAMA</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>NET NOW S.A.</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>78.112.170-3</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr"/>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M101" s="2" t="n">
+        <v>8901.08</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2322-448-CM26</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>69.030.500-3</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE VALLENAR</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>PC FACTORY</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>78.885.550-8</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr"/>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M102" s="2" t="n">
+        <v>828.24</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2859-601-CM26</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>71.236.700-8</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE ATACAMA</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>COMPUTACION INTEGRAL S A</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>96.689.970-0</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr"/>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M103" s="2" t="n">
+        <v>4936.07</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2322-527-CM26</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>69.030.500-3</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE VALLENAR</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>PRODATA S.A</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>79.808.810-6</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr"/>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M104" s="2" t="n">
+        <v>986.15</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2859-778-CM26</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>71.236.700-8</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE ATACAMA</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>ARTEC INVERSIONES LIMITADA</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>76.416.101-7</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr"/>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M105" s="2" t="n">
+        <v>28355.32</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2859-784-CM26</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>71.236.700-8</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE ATACAMA</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>77.108.316-1</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr"/>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M106" s="2" t="n">
+        <v>11890.24</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>511505-275-CM26</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>71.236.700-8</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE ATACAMA</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>NET NOW S.A.</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>78.112.170-3</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr"/>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M107" s="2" t="n">
+        <v>2268</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2859-811-CM26</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>71.236.700-8</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE ATACAMA</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>BOOKCOMPUTER</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>76.376.530-k</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr"/>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M108" s="2" t="n">
+        <v>4235.51</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2859-813-CM26</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>71.236.700-8</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE ATACAMA</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>LECHNER S.A</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>78.114.650-1</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr"/>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M109" s="2" t="n">
         <v>2478.96</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2859-888-CM26</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>71.236.700-8</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE ATACAMA</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA TODOCLICK SPA</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>76.977.985-K</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr"/>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M110" s="2" t="n">
+        <v>7182.45</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>511505-313-CM26</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>71.236.700-8</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE ATACAMA</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>NET NOW S.A.</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>78.112.170-3</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr"/>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M111" s="2" t="n">
+        <v>1134</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/venta-y-arriendo-de-computadores-y-accesorios/atacama.xlsx
+++ b/docs/oc-regiones/venta-y-arriendo-de-computadores-y-accesorios/atacama.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M111"/>
+  <dimension ref="A1:M119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -697,7 +697,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1171166-31-CM25</t>
+          <t>1172445-38-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -737,12 +737,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
+          <t>TIC SERVICES SPA</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>76.799.430-3</t>
+          <t>76.423.634-3</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>7700.49</v>
+        <v>34461.92</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1172445-38-CM25</t>
+          <t>1171166-31-CM25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -798,12 +798,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>TIC SERVICES SPA</t>
+          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>76.423.634-3</t>
+          <t>76.799.430-3</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>34461.92</v>
+        <v>7700.49</v>
       </c>
     </row>
     <row r="7">
@@ -1612,7 +1612,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>1172445-2110-CM25</t>
+          <t>1171166-204-CM25</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>37255.93</v>
+        <v>3725.59</v>
       </c>
     </row>
     <row r="21">
@@ -1734,7 +1734,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>1171166-204-CM25</t>
+          <t>1172445-2110-CM25</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1789,7 +1789,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>3725.59</v>
+        <v>37255.93</v>
       </c>
     </row>
     <row r="23">
@@ -1917,7 +1917,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2380-979-CM25</t>
+          <t>2380-978-CM25</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1972,13 +1972,13 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>10445.03</v>
+        <v>2777.89</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2380-978-CM25</t>
+          <t>2380-979-CM25</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2033,13 +2033,13 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>2777.89</v>
+        <v>10445.03</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>4631-40-CM25</t>
+          <t>1172445-2146-CM25</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2059,17 +2059,17 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>69.030.200-4</t>
+          <t>62.000.810-9</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COPIAPO</t>
+          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2079,12 +2079,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TODOTABLET SPA</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>76.292.976-7</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
@@ -2094,13 +2094,13 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>3272.5</v>
+        <v>4253.35</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>1172445-2146-CM25</t>
+          <t>4631-40-CM25</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2120,17 +2120,17 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>62.000.810-9</t>
+          <t>69.030.200-4</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
+          <t>I MUNICIPALIDAD DE COPIAPO</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>COMERCIALIZADORA TODOTABLET SPA</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>76.292.976-7</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>4253.35</v>
+        <v>3272.5</v>
       </c>
     </row>
     <row r="29">
@@ -2283,7 +2283,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2380-1098-CM25</t>
+          <t>2380-1099-CM25</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2338,13 +2338,13 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>8181.25</v>
+        <v>2454.38</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2380-1099-CM25</t>
+          <t>2380-1098-CM25</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2399,7 +2399,7 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>2454.38</v>
+        <v>8181.25</v>
       </c>
     </row>
     <row r="33">
@@ -2649,7 +2649,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2380-1430-CM25</t>
+          <t>2380-1348-CM25</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2689,12 +2689,12 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>INTEGRACION DE SOLUCIONES LIMITADA</t>
+          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>76.128.275-1</t>
+          <t>76.799.430-3</t>
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
@@ -2704,13 +2704,13 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>2809.52</v>
+        <v>10899.07</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2380-1348-CM25</t>
+          <t>2380-1430-CM25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
+          <t>INTEGRACION DE SOLUCIONES LIMITADA</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>76.799.430-3</t>
+          <t>76.128.275-1</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>10899.07</v>
+        <v>2809.52</v>
       </c>
     </row>
     <row r="39">
@@ -3669,7 +3669,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Tic Services SPA</t>
+          <t>TIC SERVICES SPA</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -3690,7 +3690,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>1171166-456-CM25</t>
+          <t>1171166-457-CM25</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3730,7 +3730,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Tic Services SPA</t>
+          <t>TIC SERVICES SPA</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -3745,13 +3745,13 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>24552.08</v>
+        <v>8593.23</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>1171166-457-CM25</t>
+          <t>1171166-456-CM25</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3791,7 +3791,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Tic Services SPA</t>
+          <t>TIC SERVICES SPA</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -3806,13 +3806,13 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>8593.23</v>
+        <v>24552.08</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>952751-18-CM25</t>
+          <t>2859-1560-CM25</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3827,22 +3827,22 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>74.269.600-6</t>
+          <t>71.236.700-8</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>DIRECCIÓN DE ADMINISTRACIÓN DE SALUD DAS</t>
+          <t>UNIVERSIDAD DE ATACAMA</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3852,12 +3852,12 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Tic Services SPA</t>
+          <t>Sociedad Comercial Infostore Ltda</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>76.423.634-3</t>
+          <t>76.131.929-9</t>
         </is>
       </c>
       <c r="K56" t="inlineStr"/>
@@ -3867,13 +3867,13 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>3362.35</v>
+        <v>49479.56</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2859-1560-CM25</t>
+          <t>1088-155-CM25</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3888,22 +3888,22 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>71.236.700-8</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE ATACAMA</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -3913,12 +3913,12 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Sociedad Comercial Infostore Ltda</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>76.131.929-9</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K57" t="inlineStr"/>
@@ -3928,13 +3928,13 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>49479.56</v>
+        <v>5383.56</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>1088-155-CM25</t>
+          <t>2859-1623-CM25</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3949,22 +3949,22 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>71.236.700-8</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>UNIVERSIDAD DE ATACAMA</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -3989,18 +3989,18 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>5383.56</v>
+        <v>19554.68</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2859-1623-CM25</t>
+          <t>2380-2656-CM25</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2239-1-LR24</t>
+          <t>2239-5-LR25</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -4010,22 +4010,22 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>71.236.700-8</t>
+          <t>69.030.200-4</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE ATACAMA</t>
+          <t>I MUNICIPALIDAD DE COPIAPO</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4035,12 +4035,12 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>ALEMED SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>77.727.285-3</t>
         </is>
       </c>
       <c r="K59" t="inlineStr"/>
@@ -4050,43 +4050,43 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>19554.68</v>
+        <v>62134.11</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>952751-20-CM25</t>
+          <t>2859-1875-CM25</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2239-1-LR24</t>
+          <t>2239-5-LR25</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>74.269.600-6</t>
+          <t>71.236.700-8</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>DIRECCIÓN DE ADMINISTRACIÓN DE SALUD DAS</t>
+          <t>UNIVERSIDAD DE ATACAMA</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4096,12 +4096,12 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Tic Services SPA</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>76.423.634-3</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K60" t="inlineStr"/>
@@ -4111,43 +4111,43 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>21538.7</v>
+        <v>7973.95</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>952751-21-CM25</t>
+          <t>1133261-201-CM25</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2239-1-LR24</t>
+          <t>2239-5-LR25</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>74.269.600-6</t>
+          <t>62.000.810-9</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>DIRECCIÓN DE ADMINISTRACIÓN DE SALUD DAS</t>
+          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -4157,12 +4157,12 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Sumatec Ltda.</t>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>76.367.430-4</t>
+          <t>77.474.803-2</t>
         </is>
       </c>
       <c r="K61" t="inlineStr"/>
@@ -4172,13 +4172,13 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>3600.8</v>
+        <v>12814.16</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2380-2656-CM25</t>
+          <t>4631-159-CM25</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4188,12 +4188,12 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>ALEMED SOLUCIONES INTEGRALES SPA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>77.727.285-3</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K62" t="inlineStr"/>
@@ -4233,13 +4233,13 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>62134.11</v>
+        <v>16944.61</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2859-1875-CM25</t>
+          <t>4631-160-CM25</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4254,22 +4254,22 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>71.236.700-8</t>
+          <t>69.030.200-4</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE ATACAMA</t>
+          <t>I MUNICIPALIDAD DE COPIAPO</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -4279,12 +4279,12 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>ALEMED SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>77.727.285-3</t>
         </is>
       </c>
       <c r="K63" t="inlineStr"/>
@@ -4294,13 +4294,13 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>7973.95</v>
+        <v>12588.01</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>1133261-201-CM25</t>
+          <t>2859-1961-CM25</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4315,7 +4315,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -4325,12 +4325,12 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>62.000.810-9</t>
+          <t>71.236.700-8</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
+          <t>UNIVERSIDAD DE ATACAMA</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -4340,12 +4340,12 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+          <t>Sociedad Comercial Infostore Ltda</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>77.474.803-2</t>
+          <t>76.131.929-9</t>
         </is>
       </c>
       <c r="K64" t="inlineStr"/>
@@ -4355,13 +4355,13 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>12814.16</v>
+        <v>8168.52</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>4631-159-CM25</t>
+          <t>751-1566-CM25</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4376,22 +4376,22 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>69.030.200-4</t>
+          <t>72.232.200-2</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COPIAPO</t>
+          <t>GOBIERNO REGIONAL DE ATACAMA</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -4401,12 +4401,12 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>COMPUTACION E INGENIERIA S A</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>96.693.120-5</t>
         </is>
       </c>
       <c r="K65" t="inlineStr"/>
@@ -4416,13 +4416,13 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>16944.61</v>
+        <v>7557.31</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>4631-160-CM25</t>
+          <t>1171166-498-CM25</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4437,22 +4437,22 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>69.030.200-4</t>
+          <t>62.000.810-9</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COPIAPO</t>
+          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -4462,12 +4462,12 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>ALEMED SOLUCIONES INTEGRALES SPA</t>
+          <t>TIC SERVICES SPA</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>77.727.285-3</t>
+          <t>76.423.634-3</t>
         </is>
       </c>
       <c r="K66" t="inlineStr"/>
@@ -4477,13 +4477,13 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>12588.01</v>
+        <v>55563.12</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2859-1961-CM25</t>
+          <t>2322-1936-CM25</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4498,7 +4498,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -4508,12 +4508,12 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>71.236.700-8</t>
+          <t>69.030.500-3</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE ATACAMA</t>
+          <t>I MUNICIPALIDAD DE VALLENAR</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -4523,12 +4523,12 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Sociedad Comercial Infostore Ltda</t>
+          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>76.131.929-9</t>
+          <t>76.799.430-3</t>
         </is>
       </c>
       <c r="K67" t="inlineStr"/>
@@ -4538,13 +4538,13 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>8168.52</v>
+        <v>30046.41</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>751-1566-CM25</t>
+          <t>2322-1937-CM25</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4559,7 +4559,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -4569,12 +4569,12 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>72.232.200-2</t>
+          <t>69.030.500-3</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE ATACAMA</t>
+          <t>I MUNICIPALIDAD DE VALLENAR</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -4584,12 +4584,12 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>COMPUTACION E INGENIERIA S A</t>
+          <t>COMPUNOW SPA</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>96.693.120-5</t>
+          <t>78.218.816-K</t>
         </is>
       </c>
       <c r="K68" t="inlineStr"/>
@@ -4599,13 +4599,13 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>7557.31</v>
+        <v>2566.69</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>1171166-498-CM25</t>
+          <t>2380-100-CM26</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4615,27 +4615,27 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>62.000.810-9</t>
+          <t>69.030.200-4</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
+          <t>I MUNICIPALIDAD DE COPIAPO</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -4645,12 +4645,12 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Tic Services SPA</t>
+          <t>ARTEC INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>76.423.634-3</t>
+          <t>76.416.101-7</t>
         </is>
       </c>
       <c r="K69" t="inlineStr"/>
@@ -4660,13 +4660,13 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>55563.12</v>
+        <v>35329.61</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2322-1937-CM25</t>
+          <t>2322-61-CM26</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4676,12 +4676,12 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -4706,12 +4706,12 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>COMPUNOW SPA</t>
+          <t>Clevertec</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>78.218.816-K</t>
+          <t>76.330.984-3</t>
         </is>
       </c>
       <c r="K70" t="inlineStr"/>
@@ -4721,13 +4721,13 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>2566.69</v>
+        <v>1141.44</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2322-1936-CM25</t>
+          <t>2322-161-CM26</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4737,12 +4737,12 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -4767,12 +4767,12 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
+          <t>PC FACTORY</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>76.799.430-3</t>
+          <t>78.885.550-8</t>
         </is>
       </c>
       <c r="K71" t="inlineStr"/>
@@ -4782,13 +4782,13 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>30046.41</v>
+        <v>628.3200000000001</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2380-100-CM26</t>
+          <t>1172445-30-CM26</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4798,27 +4798,27 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>69.030.200-4</t>
+          <t>62.000.810-9</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COPIAPO</t>
+          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -4828,12 +4828,12 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>ARTEC INVERSIONES LIMITADA</t>
+          <t>PC FACTORY</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>76.416.101-7</t>
+          <t>78.885.550-8</t>
         </is>
       </c>
       <c r="K72" t="inlineStr"/>
@@ -4843,13 +4843,13 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>35329.61</v>
+        <v>3298.68</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2322-61-CM26</t>
+          <t>1028871-194-CM26</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -4859,12 +4859,12 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>69.030.500-3</t>
+          <t>61.999.330-6</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VALLENAR</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE HUASCO</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Clevertec</t>
+          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>76.330.984-3</t>
+          <t>77.108.316-1</t>
         </is>
       </c>
       <c r="K73" t="inlineStr"/>
@@ -4904,13 +4904,13 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>1141.44</v>
+        <v>74978.47</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2322-161-CM26</t>
+          <t>1028871-197-CM26</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -4925,7 +4925,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -4935,12 +4935,12 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>69.030.500-3</t>
+          <t>61.999.330-6</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VALLENAR</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE HUASCO</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -4950,12 +4950,12 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>PC FACTORY</t>
+          <t>Sociedad Comercial Infostore Ltda</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>78.885.550-8</t>
+          <t>76.131.929-9</t>
         </is>
       </c>
       <c r="K74" t="inlineStr"/>
@@ -4965,13 +4965,13 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>628.3200000000001</v>
+        <v>24147.03</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>1172445-30-CM26</t>
+          <t>4190-68-CM26</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -4986,22 +4986,22 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>62.000.810-9</t>
+          <t>69.030.300-0</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
+          <t>I MUNICIPALIDAD DE CALDERA</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -5011,12 +5011,12 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>PC FACTORY</t>
+          <t>SYSCAM TECHNOLOGIES SPA</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>78.885.550-8</t>
+          <t>77.137.827-7</t>
         </is>
       </c>
       <c r="K75" t="inlineStr"/>
@@ -5026,13 +5026,13 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>3298.68</v>
+        <v>2315.47</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>1028871-194-CM26</t>
+          <t>2380-573-CM26</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -5042,27 +5042,27 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>61.999.330-6</t>
+          <t>69.030.200-4</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE HUASCO</t>
+          <t>I MUNICIPALIDAD DE COPIAPO</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -5072,12 +5072,12 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>77.108.316-1</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K76" t="inlineStr"/>
@@ -5087,13 +5087,13 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>74978.47</v>
+        <v>5537.03</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>1028871-197-CM26</t>
+          <t>2380-624-CM26</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -5103,27 +5103,27 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>61.999.330-6</t>
+          <t>69.030.200-4</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE HUASCO</t>
+          <t>I MUNICIPALIDAD DE COPIAPO</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Sociedad Comercial Infostore Ltda</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>76.131.929-9</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K77" t="inlineStr"/>
@@ -5148,13 +5148,13 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>24147.03</v>
+        <v>2011.15</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>4190-68-CM26</t>
+          <t>1172445-45-CM26</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -5164,27 +5164,27 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>69.030.300-0</t>
+          <t>62.000.810-9</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CALDERA</t>
+          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -5194,12 +5194,12 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>SYSCAM TECHNOLOGIES SPA</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>77.137.827-7</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K78" t="inlineStr"/>
@@ -5209,13 +5209,13 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>2315.47</v>
+        <v>27517.02</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2380-573-CM26</t>
+          <t>2859-255-CM26</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -5230,22 +5230,22 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>69.030.200-4</t>
+          <t>71.236.700-8</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COPIAPO</t>
+          <t>UNIVERSIDAD DE ATACAMA</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -5255,12 +5255,12 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K79" t="inlineStr"/>
@@ -5270,13 +5270,13 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>5537.03</v>
+        <v>1042.39</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2380-624-CM26</t>
+          <t>2859-254-CM26</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -5291,22 +5291,22 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>69.030.200-4</t>
+          <t>71.236.700-8</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COPIAPO</t>
+          <t>UNIVERSIDAD DE ATACAMA</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -5316,12 +5316,12 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>AURA XD SPA</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>76.359.312-6</t>
         </is>
       </c>
       <c r="K80" t="inlineStr"/>
@@ -5331,13 +5331,13 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>2011.15</v>
+        <v>7997.85</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>1172445-45-CM26</t>
+          <t>511505-95-CM26</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -5352,22 +5352,22 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>62.000.810-9</t>
+          <t>71.236.700-8</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
+          <t>UNIVERSIDAD DE ATACAMA</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -5377,12 +5377,12 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>Sumatec Ltda.</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>76.367.430-4</t>
         </is>
       </c>
       <c r="K81" t="inlineStr"/>
@@ -5392,13 +5392,13 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>27517.02</v>
+        <v>2690.46</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2859-254-CM26</t>
+          <t>751-169-CM26</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -5408,27 +5408,27 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>71.236.700-8</t>
+          <t>72.232.200-2</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE ATACAMA</t>
+          <t>GOBIERNO REGIONAL DE ATACAMA</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -5438,12 +5438,12 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t xml:space="preserve">AURA XD SPA </t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>76.359.312-6</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K82" t="inlineStr"/>
@@ -5453,13 +5453,13 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>7997.85</v>
+        <v>20869.29</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2859-255-CM26</t>
+          <t>751-171-CM26</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -5469,27 +5469,27 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>71.236.700-8</t>
+          <t>72.232.200-2</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE ATACAMA</t>
+          <t>GOBIERNO REGIONAL DE ATACAMA</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -5499,12 +5499,12 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K83" t="inlineStr"/>
@@ -5514,13 +5514,13 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>1042.39</v>
+        <v>4789.75</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>511505-95-CM26</t>
+          <t>1171166-161-CM26</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -5530,27 +5530,27 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>71.236.700-8</t>
+          <t>62.000.810-9</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE ATACAMA</t>
+          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -5560,12 +5560,12 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>Sumatec Ltda.</t>
+          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>76.367.430-4</t>
+          <t>76.799.430-3</t>
         </is>
       </c>
       <c r="K84" t="inlineStr"/>
@@ -5575,13 +5575,13 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>2690.46</v>
+        <v>16922.97</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>751-169-CM26</t>
+          <t>2859-390-CM26</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -5596,22 +5596,22 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>72.232.200-2</t>
+          <t>71.236.700-8</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE ATACAMA</t>
+          <t>UNIVERSIDAD DE ATACAMA</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -5621,12 +5621,12 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K85" t="inlineStr"/>
@@ -5636,13 +5636,13 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>20869.29</v>
+        <v>8144.36</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>751-171-CM26</t>
+          <t>1133261-65-CM26</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -5657,22 +5657,22 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>72.232.200-2</t>
+          <t>62.000.810-9</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE ATACAMA</t>
+          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -5682,12 +5682,12 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>76.799.430-3</t>
         </is>
       </c>
       <c r="K86" t="inlineStr"/>
@@ -5697,13 +5697,13 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>4789.75</v>
+        <v>2720.34</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>1171166-161-CM26</t>
+          <t>1133261-63-CM26</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -5718,7 +5718,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -5743,12 +5743,12 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
+          <t>COMERCIALIZADORA IGESCOM SPA</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>76.799.430-3</t>
+          <t>77.152.668-3</t>
         </is>
       </c>
       <c r="K87" t="inlineStr"/>
@@ -5758,13 +5758,13 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>16922.97</v>
+        <v>1856.4</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2859-390-CM26</t>
+          <t>1133261-64-CM26</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -5779,7 +5779,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -5789,12 +5789,12 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>71.236.700-8</t>
+          <t>62.000.810-9</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE ATACAMA</t>
+          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>VENTA, COMPRAS DE EQUIPOS &amp; ACCESORIOS TECNOLOGICOS SPA</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>77.508.642-4</t>
         </is>
       </c>
       <c r="K88" t="inlineStr"/>
@@ -5819,13 +5819,13 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>8144.36</v>
+        <v>6675.78</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>1133261-65-CM26</t>
+          <t>2322-325-CM26</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -5850,12 +5850,12 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>62.000.810-9</t>
+          <t>69.030.500-3</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
+          <t>I MUNICIPALIDAD DE VALLENAR</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -5865,12 +5865,12 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>76.799.430-3</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K89" t="inlineStr"/>
@@ -5880,13 +5880,13 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>2720.34</v>
+        <v>4568.89</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>1133261-63-CM26</t>
+          <t>2322-327-CM26</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -5911,12 +5911,12 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>62.000.810-9</t>
+          <t>69.030.500-3</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
+          <t>I MUNICIPALIDAD DE VALLENAR</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -5926,12 +5926,12 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA IGESCOM SPA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>77.152.668-3</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K90" t="inlineStr"/>
@@ -5941,13 +5941,13 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>1856.4</v>
+        <v>1337.32</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>1133261-64-CM26</t>
+          <t>5350-951-CM26</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -5962,22 +5962,22 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>62.000.810-9</t>
+          <t>69.030.500-3</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
+          <t>I MUNICIPALIDAD DE VALLENAR</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -5987,12 +5987,12 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>VENTA, COMPRAS DE EQUIPOS &amp; ACCESORIOS TECNOLOGICOS SPA</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>77.508.642-4</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K91" t="inlineStr"/>
@@ -6002,13 +6002,13 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>6675.78</v>
+        <v>22176.03</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2322-325-CM26</t>
+          <t>5350-952-CM26</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -6023,12 +6023,12 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -6063,13 +6063,13 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>4568.89</v>
+        <v>4800.76</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2322-327-CM26</t>
+          <t>2380-971-CM26</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -6079,27 +6079,27 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>69.030.500-3</t>
+          <t>69.030.200-4</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VALLENAR</t>
+          <t>I MUNICIPALIDAD DE COPIAPO</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -6109,12 +6109,12 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K93" t="inlineStr"/>
@@ -6124,13 +6124,13 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>1337.32</v>
+        <v>755.64</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>5350-951-CM26</t>
+          <t>2322-395-CM26</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -6140,17 +6140,17 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -6170,12 +6170,12 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>77.108.316-1</t>
         </is>
       </c>
       <c r="K94" t="inlineStr"/>
@@ -6185,13 +6185,13 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>22176.03</v>
+        <v>761.45</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>5350-952-CM26</t>
+          <t>2859-459-CM26</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -6201,27 +6201,27 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>69.030.500-3</t>
+          <t>71.236.700-8</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VALLENAR</t>
+          <t>UNIVERSIDAD DE ATACAMA</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -6231,12 +6231,12 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>76.075.901-5</t>
         </is>
       </c>
       <c r="K95" t="inlineStr"/>
@@ -6246,13 +6246,13 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>4800.76</v>
+        <v>16998.51</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2380-971-CM26</t>
+          <t>2381-668-CM26</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -6272,7 +6272,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -6292,12 +6292,12 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>76.075.901-5</t>
         </is>
       </c>
       <c r="K96" t="inlineStr"/>
@@ -6307,13 +6307,13 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>755.64</v>
+        <v>4439.79</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2322-395-CM26</t>
+          <t>2322-417-CM26</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -6328,12 +6328,12 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -6353,12 +6353,12 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
+          <t>COMERCIALIZADORA TODOCLICK SPA</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>77.108.316-1</t>
+          <t>76.977.985-K</t>
         </is>
       </c>
       <c r="K97" t="inlineStr"/>
@@ -6368,13 +6368,13 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>761.45</v>
+        <v>2110.32</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2859-459-CM26</t>
+          <t>511505-196-CM26</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -6389,12 +6389,12 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -6414,12 +6414,12 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>76.075.901-5</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K98" t="inlineStr"/>
@@ -6429,13 +6429,13 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>16998.51</v>
+        <v>8901.08</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2381-668-CM26</t>
+          <t>2322-448-CM26</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -6450,7 +6450,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -6460,12 +6460,12 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>69.030.200-4</t>
+          <t>69.030.500-3</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COPIAPO</t>
+          <t>I MUNICIPALIDAD DE VALLENAR</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -6475,12 +6475,12 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
+          <t>PC FACTORY</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>76.075.901-5</t>
+          <t>78.885.550-8</t>
         </is>
       </c>
       <c r="K99" t="inlineStr"/>
@@ -6490,13 +6490,13 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>4439.79</v>
+        <v>828.24</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2322-417-CM26</t>
+          <t>2859-601-CM26</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -6511,7 +6511,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -6521,12 +6521,12 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>69.030.500-3</t>
+          <t>71.236.700-8</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VALLENAR</t>
+          <t>UNIVERSIDAD DE ATACAMA</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -6536,12 +6536,12 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TODOCLICK SPA</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>76.977.985-K</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K100" t="inlineStr"/>
@@ -6551,13 +6551,13 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>2110.32</v>
+        <v>4936.07</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>511505-196-CM26</t>
+          <t>2322-527-CM26</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -6567,12 +6567,12 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -6582,12 +6582,12 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>71.236.700-8</t>
+          <t>69.030.500-3</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE ATACAMA</t>
+          <t>I MUNICIPALIDAD DE VALLENAR</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -6597,12 +6597,12 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>PRODATA S.A</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>79.808.810-6</t>
         </is>
       </c>
       <c r="K101" t="inlineStr"/>
@@ -6612,13 +6612,13 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>8901.08</v>
+        <v>986.15</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2322-448-CM26</t>
+          <t>2859-778-CM26</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -6628,12 +6628,12 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -6643,12 +6643,12 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>69.030.500-3</t>
+          <t>71.236.700-8</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VALLENAR</t>
+          <t>UNIVERSIDAD DE ATACAMA</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -6658,12 +6658,12 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>PC FACTORY</t>
+          <t>ARTEC INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>78.885.550-8</t>
+          <t>76.416.101-7</t>
         </is>
       </c>
       <c r="K102" t="inlineStr"/>
@@ -6673,13 +6673,13 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>828.24</v>
+        <v>28355.32</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2859-601-CM26</t>
+          <t>2859-784-CM26</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -6689,12 +6689,12 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>77.108.316-1</t>
         </is>
       </c>
       <c r="K103" t="inlineStr"/>
@@ -6734,13 +6734,13 @@
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>4936.07</v>
+        <v>11890.24</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2322-527-CM26</t>
+          <t>511505-275-CM26</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -6755,7 +6755,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -6765,12 +6765,12 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>69.030.500-3</t>
+          <t>71.236.700-8</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VALLENAR</t>
+          <t>UNIVERSIDAD DE ATACAMA</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -6780,12 +6780,12 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>PRODATA S.A</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>79.808.810-6</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K104" t="inlineStr"/>
@@ -6795,13 +6795,13 @@
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>986.15</v>
+        <v>2268</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2859-778-CM26</t>
+          <t>2859-811-CM26</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -6816,12 +6816,12 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -6841,12 +6841,12 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>ARTEC INVERSIONES LIMITADA</t>
+          <t>BOOKCOMPUTER</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>76.416.101-7</t>
+          <t>76.376.530-k</t>
         </is>
       </c>
       <c r="K105" t="inlineStr"/>
@@ -6856,13 +6856,13 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>28355.32</v>
+        <v>4235.51</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2859-784-CM26</t>
+          <t>2859-813-CM26</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -6877,7 +6877,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -6902,12 +6902,12 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>77.108.316-1</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K106" t="inlineStr"/>
@@ -6917,13 +6917,13 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>11890.24</v>
+        <v>2478.96</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>511505-275-CM26</t>
+          <t>2859-888-CM26</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -6933,12 +6933,12 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>ago-2026</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>COMERCIALIZADORA TODOCLICK SPA</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>76.977.985-K</t>
         </is>
       </c>
       <c r="K107" t="inlineStr"/>
@@ -6978,13 +6978,13 @@
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>2268</v>
+        <v>7182.45</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2859-811-CM26</t>
+          <t>511505-313-CM26</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -6994,12 +6994,12 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>ago-2026</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -7024,12 +7024,12 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>76.376.530-k</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K108" t="inlineStr"/>
@@ -7039,13 +7039,13 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>4235.51</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2859-813-CM26</t>
+          <t>411-392-CM26</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -7055,12 +7055,12 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>sep-2026</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -7070,12 +7070,12 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>71.236.700-8</t>
+          <t>69.251.900-0</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE ATACAMA</t>
+          <t>ILUSTRE MUNICIPALIDAD DE ALTO DEL CARMEN</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -7100,13 +7100,13 @@
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>2478.96</v>
+        <v>4957.92</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2859-888-CM26</t>
+          <t>411-393-CM26</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -7116,12 +7116,12 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>sep-2026</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -7131,12 +7131,12 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>71.236.700-8</t>
+          <t>69.251.900-0</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE ATACAMA</t>
+          <t>ILUSTRE MUNICIPALIDAD DE ALTO DEL CARMEN</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -7146,12 +7146,12 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TODOCLICK SPA</t>
+          <t>VENTA, COMPRAS DE EQUIPOS &amp; ACCESORIOS TECNOLOGICOS SPA</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>76.977.985-K</t>
+          <t>77.508.642-4</t>
         </is>
       </c>
       <c r="K110" t="inlineStr"/>
@@ -7161,13 +7161,13 @@
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>7182.45</v>
+        <v>10507.46</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>511505-313-CM26</t>
+          <t>2035-42-CM26</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -7177,12 +7177,12 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>sep-2026</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -7192,12 +7192,12 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>71.236.700-8</t>
+          <t>60.511.032-0</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE ATACAMA</t>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE CHAÑARAL</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -7207,12 +7207,12 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>RICOH</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>96.513.980-k</t>
         </is>
       </c>
       <c r="K111" t="inlineStr"/>
@@ -7222,7 +7222,495 @@
         </is>
       </c>
       <c r="M111" s="2" t="n">
+        <v>3152.31</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>1612-107-CM26</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>60.511.030-4</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE ATACAMA</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>RICOH</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>96.513.980-k</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr"/>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M112" s="2" t="n">
+        <v>3152.31</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>233-59-CM26</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>60.511.033-9</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE HUASCO</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>RICOH</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>96.513.980-k</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr"/>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M113" s="2" t="n">
+        <v>3152.31</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>2322-751-CM26</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>69.030.500-3</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE VALLENAR</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>NET NOW S.A.</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>78.112.170-3</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr"/>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M114" s="2" t="n">
         <v>1134</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>1552-460-CM26</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>61.606.300-6</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ATACAMA</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>NET NOW S.A.</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>78.112.170-3</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr"/>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M115" s="2" t="n">
+        <v>46669.29</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>2380-1682-CM26</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>69.030.200-4</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE COPIAPO</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>76.799.430-3</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr"/>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M116" s="2" t="n">
+        <v>4403.81</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>2380-1685-CM26</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>69.030.200-4</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE COPIAPO</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>FRANCO</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>76.139.769-9</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr"/>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M117" s="2" t="n">
+        <v>1939.94</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>2380-1681-CM26</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>69.030.200-4</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE COPIAPO</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>NET NOW S.A.</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>78.112.170-3</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr"/>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M118" s="2" t="n">
+        <v>7910.05</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>2859-1047-CM26</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>71.236.700-8</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE ATACAMA</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>NET NOW S.A.</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>78.112.170-3</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr"/>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M119" s="2" t="n">
+        <v>6328.04</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/venta-y-arriendo-de-computadores-y-accesorios/atacama.xlsx
+++ b/docs/oc-regiones/venta-y-arriendo-de-computadores-y-accesorios/atacama.xlsx
@@ -562,7 +562,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -623,7 +627,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -684,7 +692,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -745,7 +757,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -806,7 +822,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -867,7 +887,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -989,7 +1013,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1050,7 +1078,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1111,7 +1143,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1172,7 +1208,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1294,7 +1334,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1355,7 +1399,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1416,7 +1464,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1477,7 +1529,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1660,7 +1716,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1721,7 +1781,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1782,7 +1846,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2087,7 +2155,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2209,7 +2281,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2270,7 +2346,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2575,7 +2655,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2636,7 +2720,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2697,7 +2785,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2758,7 +2850,11 @@
           <t>76.128.275-1</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2941,7 +3037,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3002,7 +3102,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3063,7 +3167,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3189,7 +3297,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3250,7 +3362,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L46" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3311,7 +3427,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3372,7 +3492,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L48" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3433,7 +3557,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3555,7 +3683,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L51" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3616,7 +3748,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L52" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3677,7 +3813,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3738,7 +3878,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L54" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3799,7 +3943,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L55" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3921,7 +4069,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L57" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3982,7 +4134,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L58" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4043,7 +4199,11 @@
           <t>77.727.285-3</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L59" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4104,7 +4264,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L60" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4165,7 +4329,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L61" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4226,7 +4394,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L62" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4287,7 +4459,11 @@
           <t>77.727.285-3</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L63" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4409,7 +4585,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L65" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4470,7 +4650,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L66" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4531,7 +4715,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L67" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4592,7 +4780,11 @@
           <t>78.218.816-K</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L68" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4653,7 +4845,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr"/>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L69" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4897,7 +5093,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr"/>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L73" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5019,7 +5219,11 @@
           <t>77.137.827-7</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr"/>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L75" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5080,7 +5284,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L76" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5141,7 +5349,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr"/>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L77" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5202,7 +5414,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr"/>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L78" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5263,7 +5479,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr"/>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L79" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5446,7 +5666,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr"/>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L82" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5507,7 +5731,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr"/>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L83" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5568,7 +5796,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr"/>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L84" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5629,7 +5861,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr"/>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L85" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5690,7 +5926,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr"/>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L86" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5812,7 +6052,11 @@
           <t>77.508.642-4</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr"/>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L88" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5873,7 +6117,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr"/>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L89" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5934,7 +6182,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K90" t="inlineStr"/>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L90" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5995,7 +6247,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr"/>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L91" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6056,7 +6312,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr"/>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L92" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6117,7 +6377,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr"/>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L93" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6178,7 +6442,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K94" t="inlineStr"/>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L94" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6361,7 +6629,11 @@
           <t>76.977.985-K</t>
         </is>
       </c>
-      <c r="K97" t="inlineStr"/>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L97" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6422,7 +6694,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K98" t="inlineStr"/>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L98" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6544,7 +6820,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K100" t="inlineStr"/>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L100" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6605,7 +6885,11 @@
           <t>79.808.810-6</t>
         </is>
       </c>
-      <c r="K101" t="inlineStr"/>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L101" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6666,7 +6950,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K102" t="inlineStr"/>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L102" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6727,7 +7015,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K103" t="inlineStr"/>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L103" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6788,7 +7080,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K104" t="inlineStr"/>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L104" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6849,7 +7145,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K105" t="inlineStr"/>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L105" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6910,7 +7210,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K106" t="inlineStr"/>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L106" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6971,7 +7275,11 @@
           <t>76.977.985-K</t>
         </is>
       </c>
-      <c r="K107" t="inlineStr"/>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L107" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7032,7 +7340,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K108" t="inlineStr"/>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L108" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7093,7 +7405,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K109" t="inlineStr"/>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L109" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7154,7 +7470,11 @@
           <t>77.508.642-4</t>
         </is>
       </c>
-      <c r="K110" t="inlineStr"/>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L110" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7215,7 +7535,11 @@
           <t>96.513.980-k</t>
         </is>
       </c>
-      <c r="K111" t="inlineStr"/>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L111" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7276,7 +7600,11 @@
           <t>96.513.980-k</t>
         </is>
       </c>
-      <c r="K112" t="inlineStr"/>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L112" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7337,7 +7665,11 @@
           <t>96.513.980-k</t>
         </is>
       </c>
-      <c r="K113" t="inlineStr"/>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L113" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7398,7 +7730,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K114" t="inlineStr"/>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L114" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7459,7 +7795,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K115" t="inlineStr"/>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L115" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7520,7 +7860,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K116" t="inlineStr"/>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L116" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7642,7 +7986,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K118" t="inlineStr"/>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L118" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7703,7 +8051,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K119" t="inlineStr"/>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L119" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-regiones/venta-y-arriendo-de-computadores-y-accesorios/atacama.xlsx
+++ b/docs/oc-regiones/venta-y-arriendo-de-computadores-y-accesorios/atacama.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M119"/>
+  <dimension ref="A1:M123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1668,7 +1668,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>1171166-204-CM25</t>
+          <t>1172445-2110-CM25</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1727,7 +1727,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>3725.59</v>
+        <v>37255.93</v>
       </c>
     </row>
     <row r="21">
@@ -1798,7 +1798,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>1172445-2110-CM25</t>
+          <t>1171166-204-CM25</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1857,7 +1857,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>37255.93</v>
+        <v>3725.59</v>
       </c>
     </row>
     <row r="23">
@@ -2107,7 +2107,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>1172445-2146-CM25</t>
+          <t>4631-40-CM25</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2127,17 +2127,17 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>62.000.810-9</t>
+          <t>69.030.200-4</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
+          <t>I MUNICIPALIDAD DE COPIAPO</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2147,32 +2147,28 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>COMERCIALIZADORA TODOTABLET SPA</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.292.976-7</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>4253.35</v>
+        <v>3272.5</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>4631-40-CM25</t>
+          <t>1172445-2146-CM25</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2192,17 +2188,17 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>69.030.200-4</t>
+          <t>62.000.810-9</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COPIAPO</t>
+          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2212,22 +2208,26 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TODOTABLET SPA</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>76.292.976-7</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr"/>
+          <t>78.114.650-1</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>3272.5</v>
+        <v>4253.35</v>
       </c>
     </row>
     <row r="29">
@@ -2363,7 +2363,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2380-1099-CM25</t>
+          <t>2380-1098-CM25</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2418,13 +2418,13 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>2454.38</v>
+        <v>8181.25</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2380-1098-CM25</t>
+          <t>2380-1099-CM25</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2479,7 +2479,7 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>8181.25</v>
+        <v>2454.38</v>
       </c>
     </row>
     <row r="33">
@@ -3249,7 +3249,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>3703-468-CM25</t>
+          <t>1028871-1323-CM25</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3269,17 +3269,17 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>69.030.700-6</t>
+          <t>61.999.330-6</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE HUASCO</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE HUASCO</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3289,12 +3289,12 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>76.376.530-k</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -3308,13 +3308,13 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>12255.11</v>
+        <v>10814.72</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>1028871-1323-CM25</t>
+          <t>3703-468-CM25</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3334,17 +3334,17 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>61.999.330-6</t>
+          <t>69.030.700-6</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE HUASCO</t>
+          <t>I MUNICIPALIDAD DE HUASCO</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3354,12 +3354,12 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>BOOKCOMPUTER</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>76.376.530-k</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -3373,7 +3373,7 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>10814.72</v>
+        <v>12255.11</v>
       </c>
     </row>
     <row r="47">
@@ -3830,7 +3830,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>1171166-457-CM25</t>
+          <t>1171166-456-CM25</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3889,13 +3889,13 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>8593.23</v>
+        <v>24552.08</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>1171166-456-CM25</t>
+          <t>1171166-457-CM25</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3954,7 +3954,7 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>24552.08</v>
+        <v>8593.23</v>
       </c>
     </row>
     <row r="56">
@@ -4667,7 +4667,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2322-1936-CM25</t>
+          <t>2322-1937-CM25</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4707,12 +4707,12 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
+          <t>COMPUNOW SPA</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>76.799.430-3</t>
+          <t>78.218.816-K</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -4726,13 +4726,13 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>30046.41</v>
+        <v>2566.69</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2322-1937-CM25</t>
+          <t>2322-1936-CM25</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4772,12 +4772,12 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>COMPUNOW SPA</t>
+          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>78.218.816-K</t>
+          <t>76.799.430-3</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -4791,7 +4791,7 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>2566.69</v>
+        <v>30046.41</v>
       </c>
     </row>
     <row r="69">
@@ -5943,7 +5943,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>1133261-63-CM26</t>
+          <t>1133261-64-CM26</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -5983,28 +5983,32 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA IGESCOM SPA</t>
+          <t>VENTA, COMPRAS DE EQUIPOS &amp; ACCESORIOS TECNOLOGICOS SPA</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>77.152.668-3</t>
-        </is>
-      </c>
-      <c r="K87" t="inlineStr"/>
+          <t>77.508.642-4</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L87" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>1856.4</v>
+        <v>6675.78</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>1133261-64-CM26</t>
+          <t>2322-325-CM26</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -6029,12 +6033,12 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>62.000.810-9</t>
+          <t>69.030.500-3</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
+          <t>I MUNICIPALIDAD DE VALLENAR</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -6044,12 +6048,12 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>VENTA, COMPRAS DE EQUIPOS &amp; ACCESORIOS TECNOLOGICOS SPA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>77.508.642-4</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
@@ -6063,13 +6067,13 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>6675.78</v>
+        <v>4568.89</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2322-325-CM26</t>
+          <t>2322-327-CM26</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -6128,13 +6132,13 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>4568.89</v>
+        <v>1337.32</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2322-327-CM26</t>
+          <t>1133261-63-CM26</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -6159,12 +6163,12 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>69.030.500-3</t>
+          <t>62.000.810-9</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VALLENAR</t>
+          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -6174,26 +6178,22 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>COMERCIALIZADORA IGESCOM SPA</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
-        </is>
-      </c>
-      <c r="K90" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>77.152.668-3</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr"/>
       <c r="L90" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>1337.32</v>
+        <v>1856.4</v>
       </c>
     </row>
     <row r="91">
@@ -6329,7 +6329,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2380-971-CM26</t>
+          <t>2859-459-CM26</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -6349,17 +6349,17 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>69.030.200-4</t>
+          <t>71.236.700-8</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COPIAPO</t>
+          <t>UNIVERSIDAD DE ATACAMA</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -6369,32 +6369,28 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
-        </is>
-      </c>
-      <c r="K93" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.075.901-5</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr"/>
       <c r="L93" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>755.64</v>
+        <v>16998.51</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2322-395-CM26</t>
+          <t>2381-668-CM26</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -6419,12 +6415,12 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>69.030.500-3</t>
+          <t>69.030.200-4</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VALLENAR</t>
+          <t>I MUNICIPALIDAD DE COPIAPO</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -6434,32 +6430,28 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
+          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>77.108.316-1</t>
-        </is>
-      </c>
-      <c r="K94" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.075.901-5</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr"/>
       <c r="L94" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>761.45</v>
+        <v>4439.79</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2859-459-CM26</t>
+          <t>2380-971-CM26</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -6479,17 +6471,17 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>71.236.700-8</t>
+          <t>69.030.200-4</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE ATACAMA</t>
+          <t>I MUNICIPALIDAD DE COPIAPO</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -6499,28 +6491,32 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>76.075.901-5</t>
-        </is>
-      </c>
-      <c r="K95" t="inlineStr"/>
+          <t>78.112.170-3</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L95" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>16998.51</v>
+        <v>755.64</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2381-668-CM26</t>
+          <t>2322-395-CM26</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -6545,12 +6541,12 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>69.030.200-4</t>
+          <t>69.030.500-3</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COPIAPO</t>
+          <t>I MUNICIPALIDAD DE VALLENAR</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -6560,22 +6556,26 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
+          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>76.075.901-5</t>
-        </is>
-      </c>
-      <c r="K96" t="inlineStr"/>
+          <t>77.108.316-1</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L96" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>4439.79</v>
+        <v>761.45</v>
       </c>
     </row>
     <row r="97">
@@ -7357,7 +7357,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>411-392-CM26</t>
+          <t>411-393-CM26</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -7397,12 +7397,12 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>VENTA, COMPRAS DE EQUIPOS &amp; ACCESORIOS TECNOLOGICOS SPA</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>77.508.642-4</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
@@ -7416,13 +7416,13 @@
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>4957.92</v>
+        <v>10507.46</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>411-393-CM26</t>
+          <t>411-392-CM26</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -7462,12 +7462,12 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>VENTA, COMPRAS DE EQUIPOS &amp; ACCESORIOS TECNOLOGICOS SPA</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>77.508.642-4</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
@@ -7481,13 +7481,13 @@
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>10507.46</v>
+        <v>4957.92</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2035-42-CM26</t>
+          <t>1612-107-CM26</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -7512,12 +7512,12 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>60.511.032-0</t>
+          <t>60.511.030-4</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE CHAÑARAL</t>
+          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE ATACAMA</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -7552,7 +7552,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>1612-107-CM26</t>
+          <t>2035-42-CM26</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>60.511.030-4</t>
+          <t>60.511.032-0</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE ATACAMA</t>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE CHAÑARAL</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -7637,7 +7637,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -7767,7 +7767,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -7812,7 +7812,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2380-1682-CM26</t>
+          <t>2380-1681-CM26</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -7852,12 +7852,12 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>76.799.430-3</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
@@ -7871,13 +7871,13 @@
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>4403.81</v>
+        <v>7910.05</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2380-1685-CM26</t>
+          <t>2380-1682-CM26</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -7917,28 +7917,32 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>FRANCO</t>
+          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>76.139.769-9</t>
-        </is>
-      </c>
-      <c r="K117" t="inlineStr"/>
+          <t>76.799.430-3</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L117" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>1939.94</v>
+        <v>4403.81</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2380-1681-CM26</t>
+          <t>2380-1685-CM26</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -7978,26 +7982,22 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>FRANCO</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
-        </is>
-      </c>
-      <c r="K118" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.139.769-9</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr"/>
       <c r="L118" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>7910.05</v>
+        <v>1939.94</v>
       </c>
     </row>
     <row r="119">
@@ -8063,6 +8063,262 @@
       </c>
       <c r="M119" s="2" t="n">
         <v>6328.04</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>2859-1180-CM26</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>71.236.700-8</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE ATACAMA</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>LECHNER S.A</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>78.114.650-1</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M120" s="2" t="n">
+        <v>5760.27</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>2859-1189-CM26</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>71.236.700-8</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE ATACAMA</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>COMPUTACION INTEGRAL S A</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>96.689.970-0</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M121" s="2" t="n">
+        <v>14517.33</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>2859-1222-CM26</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>71.236.700-8</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE ATACAMA</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>FRANCO</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>76.139.769-9</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr"/>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M122" s="2" t="n">
+        <v>2751.41</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>411-445-CM26</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>69.251.900-0</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>ILUSTRE MUNICIPALIDAD DE ALTO DEL CARMEN</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>96.678.350-8</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M123" s="2" t="n">
+        <v>5289.55</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/venta-y-arriendo-de-computadores-y-accesorios/atacama.xlsx
+++ b/docs/oc-regiones/venta-y-arriendo-de-computadores-y-accesorios/atacama.xlsx
@@ -6857,7 +6857,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -7117,7 +7117,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -7247,7 +7247,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">

--- a/docs/oc-regiones/venta-y-arriendo-de-computadores-y-accesorios/atacama.xlsx
+++ b/docs/oc-regiones/venta-y-arriendo-de-computadores-y-accesorios/atacama.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M123"/>
+  <dimension ref="A1:M124"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3054,7 +3054,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>1028871-1252-CM25</t>
+          <t>1028871-1250-CM25</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>TIC SERVICES SPA</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>76.423.634-3</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -3113,13 +3113,13 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>11652.48</v>
+        <v>5941.29</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>1028871-1250-CM25</t>
+          <t>1028871-1252-CM25</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3159,12 +3159,12 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>TIC SERVICES SPA</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>76.423.634-3</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -3178,7 +3178,7 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>5941.29</v>
+        <v>11652.48</v>
       </c>
     </row>
     <row r="44">
@@ -5878,7 +5878,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>1133261-65-CM26</t>
+          <t>2322-325-CM26</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -5903,12 +5903,12 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>62.000.810-9</t>
+          <t>69.030.500-3</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
+          <t>I MUNICIPALIDAD DE VALLENAR</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>76.799.430-3</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
@@ -5937,13 +5937,13 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>2720.34</v>
+        <v>4568.89</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>1133261-64-CM26</t>
+          <t>2322-327-CM26</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>62.000.810-9</t>
+          <t>69.030.500-3</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
+          <t>I MUNICIPALIDAD DE VALLENAR</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -5983,12 +5983,12 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>VENTA, COMPRAS DE EQUIPOS &amp; ACCESORIOS TECNOLOGICOS SPA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>77.508.642-4</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
@@ -6002,13 +6002,13 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>6675.78</v>
+        <v>1337.32</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2322-325-CM26</t>
+          <t>1133261-63-CM26</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>69.030.500-3</t>
+          <t>62.000.810-9</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VALLENAR</t>
+          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -6048,32 +6048,28 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>COMERCIALIZADORA IGESCOM SPA</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
-        </is>
-      </c>
-      <c r="K88" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>77.152.668-3</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr"/>
       <c r="L88" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>4568.89</v>
+        <v>1856.4</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2322-327-CM26</t>
+          <t>1133261-64-CM26</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -6098,12 +6094,12 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>69.030.500-3</t>
+          <t>62.000.810-9</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VALLENAR</t>
+          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -6113,12 +6109,12 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>VENTA, COMPRAS DE EQUIPOS &amp; ACCESORIOS TECNOLOGICOS SPA</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>77.508.642-4</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
@@ -6132,13 +6128,13 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>1337.32</v>
+        <v>6675.78</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>1133261-63-CM26</t>
+          <t>1133261-65-CM26</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -6178,22 +6174,26 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA IGESCOM SPA</t>
+          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>77.152.668-3</t>
-        </is>
-      </c>
-      <c r="K90" t="inlineStr"/>
+          <t>76.799.430-3</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L90" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>1856.4</v>
+        <v>2720.34</v>
       </c>
     </row>
     <row r="91">
@@ -6329,7 +6329,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2859-459-CM26</t>
+          <t>2322-395-CM26</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -6354,12 +6354,12 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>71.236.700-8</t>
+          <t>69.030.500-3</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE ATACAMA</t>
+          <t>I MUNICIPALIDAD DE VALLENAR</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -6369,22 +6369,26 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
+          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>76.075.901-5</t>
-        </is>
-      </c>
-      <c r="K93" t="inlineStr"/>
+          <t>77.108.316-1</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L93" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>16998.51</v>
+        <v>761.45</v>
       </c>
     </row>
     <row r="94">
@@ -6451,7 +6455,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2380-971-CM26</t>
+          <t>2859-459-CM26</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -6471,17 +6475,17 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>69.030.200-4</t>
+          <t>71.236.700-8</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COPIAPO</t>
+          <t>UNIVERSIDAD DE ATACAMA</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -6491,32 +6495,28 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
-        </is>
-      </c>
-      <c r="K95" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.075.901-5</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr"/>
       <c r="L95" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>755.64</v>
+        <v>16998.51</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2322-395-CM26</t>
+          <t>2380-971-CM26</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -6536,17 +6536,17 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>69.030.500-3</t>
+          <t>69.030.200-4</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VALLENAR</t>
+          <t>I MUNICIPALIDAD DE COPIAPO</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -6556,12 +6556,12 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>77.108.316-1</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
@@ -6575,7 +6575,7 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>761.45</v>
+        <v>755.64</v>
       </c>
     </row>
     <row r="97">
@@ -6646,7 +6646,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>511505-196-CM26</t>
+          <t>2322-448-CM26</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -6666,17 +6666,17 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>71.236.700-8</t>
+          <t>69.030.500-3</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE ATACAMA</t>
+          <t>I MUNICIPALIDAD DE VALLENAR</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -6686,32 +6686,28 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>PC FACTORY</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
-        </is>
-      </c>
-      <c r="K98" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>78.885.550-8</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr"/>
       <c r="L98" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>8901.08</v>
+        <v>828.24</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2322-448-CM26</t>
+          <t>511505-196-CM26</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -6731,17 +6727,17 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>69.030.500-3</t>
+          <t>71.236.700-8</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VALLENAR</t>
+          <t>UNIVERSIDAD DE ATACAMA</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -6751,22 +6747,26 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>PC FACTORY</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>78.885.550-8</t>
-        </is>
-      </c>
-      <c r="K99" t="inlineStr"/>
+          <t>78.112.170-3</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L99" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>828.24</v>
+        <v>8901.08</v>
       </c>
     </row>
     <row r="100">
@@ -6902,7 +6902,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2859-778-CM26</t>
+          <t>2859-784-CM26</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -6942,12 +6942,12 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>ARTEC INVERSIONES LIMITADA</t>
+          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>76.416.101-7</t>
+          <t>77.108.316-1</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
@@ -6961,13 +6961,13 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>28355.32</v>
+        <v>11890.24</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2859-784-CM26</t>
+          <t>2859-778-CM26</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -7007,12 +7007,12 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
+          <t>ARTEC INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>77.108.316-1</t>
+          <t>76.416.101-7</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
@@ -7026,7 +7026,7 @@
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>11890.24</v>
+        <v>28355.32</v>
       </c>
     </row>
     <row r="104">
@@ -7487,7 +7487,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>1612-107-CM26</t>
+          <t>2035-42-CM26</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -7512,12 +7512,12 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>60.511.030-4</t>
+          <t>60.511.032-0</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE ATACAMA</t>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE CHAÑARAL</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -7552,7 +7552,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2035-42-CM26</t>
+          <t>233-59-CM26</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -7572,17 +7572,17 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>60.511.032-0</t>
+          <t>60.511.033-9</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE CHAÑARAL</t>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE HUASCO</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -7617,7 +7617,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>233-59-CM26</t>
+          <t>1612-107-CM26</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -7637,17 +7637,17 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>60.511.033-9</t>
+          <t>60.511.030-4</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE HUASCO</t>
+          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE ATACAMA</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -7812,7 +7812,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2380-1681-CM26</t>
+          <t>2380-1682-CM26</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -7852,12 +7852,12 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>76.799.430-3</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
@@ -7871,13 +7871,13 @@
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>7910.05</v>
+        <v>4403.81</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2380-1682-CM26</t>
+          <t>2380-1681-CM26</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -7917,12 +7917,12 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>76.799.430-3</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
@@ -7936,7 +7936,7 @@
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>4403.81</v>
+        <v>7910.05</v>
       </c>
     </row>
     <row r="118">
@@ -8198,7 +8198,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2859-1222-CM26</t>
+          <t>411-445-CM26</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -8218,17 +8218,17 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>71.236.700-8</t>
+          <t>69.251.900-0</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE ATACAMA</t>
+          <t>ILUSTRE MUNICIPALIDAD DE ALTO DEL CARMEN</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -8238,28 +8238,32 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>FRANCO</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>76.139.769-9</t>
-        </is>
-      </c>
-      <c r="K122" t="inlineStr"/>
+          <t>96.678.350-8</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L122" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>2751.41</v>
+        <v>5289.55</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>411-445-CM26</t>
+          <t>2859-1222-CM26</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -8279,46 +8283,107 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>71.236.700-8</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE ATACAMA</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>FRANCO</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>76.139.769-9</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr"/>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M123" s="2" t="n">
+        <v>2751.41</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>1028871-664-CM26</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
           <t>Aceptada</t>
         </is>
       </c>
-      <c r="F123" t="inlineStr">
-        <is>
-          <t>69.251.900-0</t>
-        </is>
-      </c>
-      <c r="G123" t="inlineStr">
-        <is>
-          <t>ILUSTRE MUNICIPALIDAD DE ALTO DEL CARMEN</t>
-        </is>
-      </c>
-      <c r="H123" t="inlineStr">
-        <is>
-          <t>Atacama</t>
-        </is>
-      </c>
-      <c r="I123" t="inlineStr">
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>61.999.330-6</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE HUASCO</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
         <is>
           <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
-      <c r="J123" t="inlineStr">
+      <c r="J124" t="inlineStr">
         <is>
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K123" t="inlineStr">
+      <c r="K124" t="inlineStr">
         <is>
           <t>Metropolitana</t>
         </is>
       </c>
-      <c r="L123" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M123" s="2" t="n">
-        <v>5289.55</v>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M124" s="2" t="n">
+        <v>14617.94</v>
       </c>
     </row>
   </sheetData>
